--- a/data/PLAYERLIST.xlsx
+++ b/data/PLAYERLIST.xlsx
@@ -496,7 +496,7 @@
     <t>P.J. Washington</t>
   </si>
   <si>
-    <t>Bobby Portis</t>
+    <t>Bobby Portis Jr.</t>
   </si>
   <si>
     <t>Sam Hauser</t>
@@ -2238,6 +2238,9 @@
       <c r="F52">
         <v>32.49</v>
       </c>
+      <c r="G52">
+        <v>19</v>
+      </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
@@ -2488,6 +2491,9 @@
       <c r="F63">
         <v>31.37</v>
       </c>
+      <c r="G63">
+        <v>20</v>
+      </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
@@ -3244,6 +3250,9 @@
       <c r="F96">
         <v>26.31</v>
       </c>
+      <c r="G96">
+        <v>19</v>
+      </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
@@ -3609,6 +3618,9 @@
       <c r="F112">
         <v>26.12</v>
       </c>
+      <c r="G112">
+        <v>24</v>
+      </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
@@ -4480,6 +4492,9 @@
       <c r="F150">
         <v>22.98</v>
       </c>
+      <c r="G150">
+        <v>21</v>
+      </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
@@ -4499,6 +4514,9 @@
       </c>
       <c r="F151">
         <v>22.97</v>
+      </c>
+      <c r="G151">
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:7">

--- a/data/PLAYERLIST.xlsx
+++ b/data/PLAYERLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_fetch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_fetch" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4366.9</v>
+        <v>4632.05</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>77.2</v>
       </c>
       <c r="F2" t="n">
-        <v>61.51</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>31</v>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3602.3</v>
+        <v>4115.2</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F3" t="n">
-        <v>54.58</v>
+        <v>54.01</v>
       </c>
       <c r="G3" t="n">
         <v>27</v>
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3524</v>
+        <v>3926</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F4" t="n">
-        <v>51.82</v>
+        <v>51.52</v>
       </c>
       <c r="G4" t="n">
         <v>22</v>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. Gilgeous-Alexander</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3367.1</v>
+        <v>3658.15</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F5" t="n">
-        <v>46.12</v>
+        <v>48.01</v>
       </c>
       <c r="G5" t="n">
         <v>28</v>
@@ -585,12 +585,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -599,187 +599,187 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3170.95</v>
+        <v>3577.8</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F6" t="n">
-        <v>46.63</v>
+        <v>46.95</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3135.25</v>
+        <v>3472.25</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
-        <v>45.44</v>
+        <v>45.09</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Giannis Antetokounmpo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3092.3</v>
+        <v>3437</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="F8" t="n">
-        <v>40.69</v>
+        <v>45.1</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Giannis Antetokounmpo</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3087.9</v>
+        <v>3430.6</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F9" t="n">
-        <v>45.41</v>
+        <v>45.02</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Domantas Sabonis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3043.2</v>
+        <v>3288.55</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F10" t="n">
-        <v>46.82</v>
+        <v>43.16</v>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2979.25</v>
+        <v>3245.55</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F11" t="n">
-        <v>39.72</v>
+        <v>42.59</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Domantas Sabonis</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2977.25</v>
+        <v>3229.55</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>77.2</v>
       </c>
       <c r="F12" t="n">
-        <v>43.15</v>
+        <v>41.83</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -788,41 +788,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Tyrese Haliburton</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2947.8</v>
+        <v>3228.5</v>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F13" t="n">
-        <v>40.38</v>
+        <v>42.37</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2936.3</v>
+        <v>3205.6</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>42.56</v>
+        <v>41.63</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2914.15</v>
+        <v>3109.6</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="F15" t="n">
-        <v>42.23</v>
+        <v>40.81</v>
       </c>
       <c r="G15" t="n">
         <v>24</v>
@@ -875,12 +875,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tyrese Haliburton</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -889,245 +889,245 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2905.5</v>
+        <v>3092.95</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F16" t="n">
-        <v>42.73</v>
+        <v>40.59</v>
       </c>
       <c r="G16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2868.4</v>
+        <v>3086.2</v>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>75.2</v>
       </c>
       <c r="F17" t="n">
-        <v>42.18</v>
+        <v>41.04</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2862.15</v>
+        <v>3084.75</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F18" t="n">
-        <v>42.09</v>
+        <v>40.48</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2854.8</v>
+        <v>3027.4</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F19" t="n">
-        <v>42.61</v>
+        <v>39.73</v>
       </c>
       <c r="G19" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2853.85</v>
+        <v>2993.15</v>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>75.2</v>
       </c>
       <c r="F20" t="n">
-        <v>38.57</v>
+        <v>39.8</v>
       </c>
       <c r="G20" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alperen Şengün</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2813.55</v>
+        <v>2967.05</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F21" t="n">
-        <v>39.08</v>
+        <v>38.94</v>
       </c>
       <c r="G21" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Alperen Şengün</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2766.45</v>
+        <v>2953.4</v>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F22" t="n">
-        <v>37.9</v>
+        <v>38.76</v>
       </c>
       <c r="G22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2743.6</v>
+        <v>2952.95</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F23" t="n">
-        <v>38.11</v>
+        <v>38.75</v>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Trae Young</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2734.75</v>
+        <v>2948.4</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F24" t="n">
-        <v>39.07</v>
+        <v>38.69</v>
       </c>
       <c r="G24" t="n">
         <v>28</v>
@@ -1136,12 +1136,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1150,158 +1150,158 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2731.55</v>
+        <v>2941.75</v>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>77.2</v>
       </c>
       <c r="F25" t="n">
-        <v>37.42</v>
+        <v>38.11</v>
       </c>
       <c r="G25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF,PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2721.75</v>
+        <v>2929.9</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>77.2</v>
       </c>
       <c r="F26" t="n">
-        <v>37.8</v>
+        <v>37.95</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2717.8</v>
+        <v>2924.15</v>
       </c>
       <c r="E27" t="n">
-        <v>76</v>
+        <v>77.2</v>
       </c>
       <c r="F27" t="n">
-        <v>35.76</v>
+        <v>37.88</v>
       </c>
       <c r="G27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2699.35</v>
+        <v>2912.2</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>77.2</v>
       </c>
       <c r="F28" t="n">
-        <v>38.02</v>
+        <v>37.72</v>
       </c>
       <c r="G28" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Trae Young</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2698.35</v>
+        <v>2907</v>
       </c>
       <c r="E29" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F29" t="n">
-        <v>39.68</v>
+        <v>38.15</v>
       </c>
       <c r="G29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2660.9</v>
+        <v>2892.45</v>
       </c>
       <c r="E30" t="n">
-        <v>70</v>
+        <v>65.5</v>
       </c>
       <c r="F30" t="n">
-        <v>38.01</v>
+        <v>44.16</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
@@ -1310,41 +1310,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2652.9</v>
+        <v>2890.1</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F31" t="n">
-        <v>35.37</v>
+        <v>37.93</v>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1353,274 +1353,274 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2651.1</v>
+        <v>2881.6</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="F32" t="n">
-        <v>44.18</v>
+        <v>37.82</v>
       </c>
       <c r="G32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Lauri Markkanen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2644.6</v>
+        <v>2877.65</v>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F33" t="n">
-        <v>36.23</v>
+        <v>37.76</v>
       </c>
       <c r="G33" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2627.5</v>
+        <v>2847.6</v>
       </c>
       <c r="E34" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F34" t="n">
-        <v>37.54</v>
+        <v>37.37</v>
       </c>
       <c r="G34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lauri Markkanen</t>
+          <t>Damian Lillard</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2612.7</v>
+        <v>2823.4</v>
       </c>
       <c r="E35" t="n">
-        <v>68</v>
+        <v>77.2</v>
       </c>
       <c r="F35" t="n">
-        <v>38.42</v>
+        <v>36.57</v>
       </c>
       <c r="G35" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N. Alexander-Walker</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2612.6</v>
+        <v>2819.95</v>
       </c>
       <c r="E36" t="n">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="F36" t="n">
-        <v>32.66</v>
+        <v>37.01</v>
       </c>
       <c r="G36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2592.2</v>
+        <v>2817</v>
       </c>
       <c r="E37" t="n">
-        <v>72</v>
+        <v>77.2</v>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>36.49</v>
       </c>
       <c r="G37" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF,C</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2589.75</v>
+        <v>2815.3</v>
       </c>
       <c r="E38" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F38" t="n">
-        <v>38.08</v>
+        <v>36.95</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Walker Kessler</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2582.05</v>
+        <v>2795.2</v>
       </c>
       <c r="E39" t="n">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="F39" t="n">
-        <v>37.42</v>
+        <v>36.68</v>
       </c>
       <c r="G39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2550.8</v>
+        <v>2780.45</v>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F40" t="n">
-        <v>36.44</v>
+        <v>36.49</v>
       </c>
       <c r="G40" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Walker Kessler</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2547.15</v>
+        <v>2776.4</v>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>77.2</v>
       </c>
       <c r="F41" t="n">
-        <v>38.02</v>
+        <v>35.96</v>
       </c>
       <c r="G41" t="n">
         <v>25</v>
@@ -1629,30 +1629,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2539</v>
+        <v>2775.35</v>
       </c>
       <c r="E42" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F42" t="n">
-        <v>34.78</v>
+        <v>36.42</v>
       </c>
       <c r="G42" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2537.3</v>
+        <v>2721.25</v>
       </c>
       <c r="E43" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
       <c r="F43" t="n">
-        <v>36.25</v>
+        <v>37.12</v>
       </c>
       <c r="G43" t="n">
         <v>22</v>
@@ -1687,215 +1687,215 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2531.85</v>
+        <v>2714.95</v>
       </c>
       <c r="E44" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F44" t="n">
-        <v>37.23</v>
+        <v>35.63</v>
       </c>
       <c r="G44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2528.8</v>
+        <v>2714.25</v>
       </c>
       <c r="E45" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F45" t="n">
-        <v>38.32</v>
+        <v>35.62</v>
       </c>
       <c r="G45" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2527.7</v>
+        <v>2705.05</v>
       </c>
       <c r="E46" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F46" t="n">
-        <v>37.17</v>
+        <v>35.5</v>
       </c>
       <c r="G46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2519.05</v>
+        <v>2698.4</v>
       </c>
       <c r="E47" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F47" t="n">
-        <v>38.17</v>
+        <v>35.41</v>
       </c>
       <c r="G47" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Kyrie Irving</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2515.8</v>
+        <v>2674.15</v>
       </c>
       <c r="E48" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F48" t="n">
-        <v>35.94</v>
+        <v>35.09</v>
       </c>
       <c r="G48" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2489.95</v>
+        <v>2661.45</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F49" t="n">
-        <v>34.58</v>
+        <v>34.93</v>
       </c>
       <c r="G49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Damian Lillard</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2468.45</v>
+        <v>2649.9</v>
       </c>
       <c r="E50" t="n">
-        <v>62</v>
+        <v>76.2</v>
       </c>
       <c r="F50" t="n">
-        <v>39.81</v>
+        <v>34.78</v>
       </c>
       <c r="G50" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1904,27 +1904,27 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2445.45</v>
+        <v>2647.4</v>
       </c>
       <c r="E51" t="n">
-        <v>71</v>
+        <v>76.2</v>
       </c>
       <c r="F51" t="n">
-        <v>34.44</v>
+        <v>34.74</v>
       </c>
       <c r="G51" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1933,651 +1933,651 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2445.3</v>
+        <v>2628</v>
       </c>
       <c r="E52" t="n">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="F52" t="n">
-        <v>35.44</v>
+        <v>34.49</v>
       </c>
       <c r="G52" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2444.45</v>
+        <v>2626.5</v>
       </c>
       <c r="E53" t="n">
-        <v>76</v>
+        <v>75.2</v>
       </c>
       <c r="F53" t="n">
-        <v>32.16</v>
+        <v>34.93</v>
       </c>
       <c r="G53" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cameron Boozer</t>
+          <t>Keyonte George</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2436.95</v>
+        <v>2592.7</v>
       </c>
       <c r="E54" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F54" t="n">
-        <v>32.49</v>
+        <v>34.02</v>
       </c>
       <c r="G54" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Ty Jerome</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2421.25</v>
+        <v>2591.1</v>
       </c>
       <c r="E55" t="n">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="F55" t="n">
-        <v>35.09</v>
+        <v>34</v>
       </c>
       <c r="G55" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2419.65</v>
+        <v>2560.35</v>
       </c>
       <c r="E56" t="n">
-        <v>69</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>35.07</v>
+        <v>33.64</v>
       </c>
       <c r="G56" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2416</v>
+        <v>2533.95</v>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F57" t="n">
-        <v>37.17</v>
+        <v>33.25</v>
       </c>
       <c r="G57" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2402.75</v>
+        <v>2532.65</v>
       </c>
       <c r="E58" t="n">
-        <v>69</v>
+        <v>77.2</v>
       </c>
       <c r="F58" t="n">
-        <v>34.82</v>
+        <v>32.81</v>
       </c>
       <c r="G58" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ivica Zubac</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2394.8</v>
+        <v>2528.2</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F59" t="n">
-        <v>33.26</v>
+        <v>33.18</v>
       </c>
       <c r="G59" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>N. Alexander-Walker</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2389.75</v>
+        <v>2509.05</v>
       </c>
       <c r="E60" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F60" t="n">
-        <v>34.14</v>
+        <v>32.93</v>
       </c>
       <c r="G60" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Anthony Davis</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2386.8</v>
+        <v>2499.6</v>
       </c>
       <c r="E61" t="n">
-        <v>58</v>
+        <v>76.2</v>
       </c>
       <c r="F61" t="n">
-        <v>41.15</v>
+        <v>32.8</v>
       </c>
       <c r="G61" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2386.4</v>
+        <v>2486.75</v>
       </c>
       <c r="E62" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F62" t="n">
-        <v>33.14</v>
+        <v>32.63</v>
       </c>
       <c r="G62" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kyrie Irving</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2344.75</v>
+        <v>2475.45</v>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>75.2</v>
       </c>
       <c r="F63" t="n">
-        <v>39.08</v>
+        <v>32.92</v>
       </c>
       <c r="G63" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2342</v>
+        <v>2466.15</v>
       </c>
       <c r="E64" t="n">
-        <v>82</v>
+        <v>76.2</v>
       </c>
       <c r="F64" t="n">
-        <v>28.56</v>
+        <v>32.36</v>
       </c>
       <c r="G64" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2337.95</v>
+        <v>2460.85</v>
       </c>
       <c r="E65" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F65" t="n">
-        <v>35.42</v>
+        <v>32.29</v>
       </c>
       <c r="G65" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Anthony Davis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2328.75</v>
+        <v>2452.15</v>
       </c>
       <c r="E66" t="n">
-        <v>65</v>
+        <v>61.6</v>
       </c>
       <c r="F66" t="n">
-        <v>35.83</v>
+        <v>39.81</v>
       </c>
       <c r="G66" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2315.35</v>
+        <v>2450.1</v>
       </c>
       <c r="E67" t="n">
-        <v>75</v>
+        <v>77.2</v>
       </c>
       <c r="F67" t="n">
-        <v>30.87</v>
+        <v>31.74</v>
       </c>
       <c r="G67" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2309.8</v>
+        <v>2446.9</v>
       </c>
       <c r="E68" t="n">
-        <v>70</v>
+        <v>70.3</v>
       </c>
       <c r="F68" t="n">
-        <v>33</v>
+        <v>34.81</v>
       </c>
       <c r="G68" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2308.9</v>
+        <v>2441.2</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>64.3</v>
       </c>
       <c r="F69" t="n">
-        <v>32.07</v>
+        <v>37.97</v>
       </c>
       <c r="G69" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Jaren Jackson Jr.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2306.6</v>
+        <v>2356.05</v>
       </c>
       <c r="E70" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F70" t="n">
-        <v>32.04</v>
+        <v>30.92</v>
       </c>
       <c r="G70" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2305.2</v>
+        <v>2346.15</v>
       </c>
       <c r="E71" t="n">
-        <v>59</v>
+        <v>76.2</v>
       </c>
       <c r="F71" t="n">
-        <v>39.07</v>
+        <v>30.79</v>
       </c>
       <c r="G71" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Keyonte George</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2304.2</v>
+        <v>2345.9</v>
       </c>
       <c r="E72" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F72" t="n">
-        <v>34.39</v>
+        <v>30.79</v>
       </c>
       <c r="G72" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2293.7</v>
+        <v>2332.75</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>77.2</v>
       </c>
       <c r="F73" t="n">
-        <v>31.86</v>
+        <v>30.22</v>
       </c>
       <c r="G73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Ivica Zubac</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2292.45</v>
+        <v>2316.95</v>
       </c>
       <c r="E74" t="n">
-        <v>71</v>
+        <v>75.2</v>
       </c>
       <c r="F74" t="n">
-        <v>32.29</v>
+        <v>30.81</v>
       </c>
       <c r="G74" t="n">
         <v>29</v>
@@ -2586,70 +2586,70 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2255.5</v>
+        <v>2305.05</v>
       </c>
       <c r="E75" t="n">
-        <v>70</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>32.22</v>
+        <v>30.29</v>
       </c>
       <c r="G75" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Caleb Wilson</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2253.3</v>
+        <v>2305</v>
       </c>
       <c r="E76" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F76" t="n">
-        <v>31.3</v>
+        <v>30.25</v>
       </c>
       <c r="G76" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2658,71 +2658,71 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2241.05</v>
+        <v>2302.1</v>
       </c>
       <c r="E77" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F77" t="n">
-        <v>30.7</v>
+        <v>30.21</v>
       </c>
       <c r="G77" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Day'Ron Sharpe</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2233.25</v>
+        <v>2298.45</v>
       </c>
       <c r="E78" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F78" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="G78" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2231.25</v>
+        <v>2285.92</v>
       </c>
       <c r="E79" t="n">
-        <v>69</v>
+        <v>77.2</v>
       </c>
       <c r="F79" t="n">
-        <v>32.34</v>
+        <v>29.61</v>
       </c>
       <c r="G79" t="n">
         <v>29</v>
@@ -2731,59 +2731,59 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Fred VanVleet</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2228.5</v>
+        <v>2252.15</v>
       </c>
       <c r="E80" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F80" t="n">
-        <v>33.77</v>
+        <v>29.56</v>
       </c>
       <c r="G80" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Egor Dëmin</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2210.45</v>
+        <v>2226.8</v>
       </c>
       <c r="E81" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F81" t="n">
-        <v>31.58</v>
+        <v>29.22</v>
       </c>
       <c r="G81" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2192.3</v>
+        <v>2226</v>
       </c>
       <c r="E82" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F82" t="n">
-        <v>30.03</v>
+        <v>29.21</v>
       </c>
       <c r="G82" t="n">
         <v>34</v>
@@ -2818,114 +2818,114 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Egor Dëmin</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2190.35</v>
+        <v>2214.15</v>
       </c>
       <c r="E83" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F83" t="n">
-        <v>30.42</v>
+        <v>29.06</v>
       </c>
       <c r="G83" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2185.95</v>
+        <v>2207.25</v>
       </c>
       <c r="E84" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F84" t="n">
-        <v>30.36</v>
+        <v>28.97</v>
       </c>
       <c r="G84" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ty Jerome</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2182.2</v>
+        <v>2205.35</v>
       </c>
       <c r="E85" t="n">
-        <v>65</v>
+        <v>77.2</v>
       </c>
       <c r="F85" t="n">
-        <v>33.57</v>
+        <v>28.57</v>
       </c>
       <c r="G85" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2181.65</v>
+        <v>2198.7</v>
       </c>
       <c r="E86" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F86" t="n">
-        <v>30.3</v>
+        <v>28.85</v>
       </c>
       <c r="G86" t="n">
         <v>24</v>
@@ -2934,157 +2934,157 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2173.1</v>
+        <v>2197.8</v>
       </c>
       <c r="E87" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F87" t="n">
-        <v>30.18</v>
+        <v>28.84</v>
       </c>
       <c r="G87" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2163.5</v>
+        <v>2195.85</v>
       </c>
       <c r="E88" t="n">
-        <v>75</v>
+        <v>77.2</v>
       </c>
       <c r="F88" t="n">
-        <v>28.85</v>
+        <v>28.44</v>
       </c>
       <c r="G88" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Jusuf Nurkić</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2150</v>
+        <v>2193.3</v>
       </c>
       <c r="E89" t="n">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="F89" t="n">
-        <v>29.45</v>
+        <v>30.34</v>
       </c>
       <c r="G89" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jaren Jackson Jr.</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2142.5</v>
+        <v>2189.85</v>
       </c>
       <c r="E90" t="n">
-        <v>66</v>
+        <v>70.3</v>
       </c>
       <c r="F90" t="n">
-        <v>32.46</v>
+        <v>31.15</v>
       </c>
       <c r="G90" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Darryn Peterson</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2136.4</v>
+        <v>2186.1</v>
       </c>
       <c r="E91" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="F91" t="n">
-        <v>29.27</v>
+        <v>29.82</v>
       </c>
       <c r="G91" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Darius Acuff Jr.</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3093,172 +3093,172 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2133.05</v>
+        <v>2172.35</v>
       </c>
       <c r="E92" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="F92" t="n">
-        <v>28.07</v>
+        <v>28.51</v>
       </c>
       <c r="G92" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2115.05</v>
+        <v>2168.9</v>
       </c>
       <c r="E93" t="n">
-        <v>71</v>
+        <v>76.2</v>
       </c>
       <c r="F93" t="n">
-        <v>29.79</v>
+        <v>28.46</v>
       </c>
       <c r="G93" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2104.5</v>
+        <v>2165.4</v>
       </c>
       <c r="E94" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F94" t="n">
-        <v>31.41</v>
+        <v>28.42</v>
       </c>
       <c r="G94" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2078.15</v>
+        <v>2150.9</v>
       </c>
       <c r="E95" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F95" t="n">
-        <v>29.69</v>
+        <v>28.23</v>
       </c>
       <c r="G95" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Keegan Murray</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2056.65</v>
+        <v>2142.35</v>
       </c>
       <c r="E96" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F96" t="n">
-        <v>29.38</v>
+        <v>28.11</v>
       </c>
       <c r="G96" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AJ Dybantsa</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2051.85</v>
+        <v>2138.3</v>
       </c>
       <c r="E97" t="n">
-        <v>78</v>
+        <v>75.2</v>
       </c>
       <c r="F97" t="n">
-        <v>26.31</v>
+        <v>28.43</v>
       </c>
       <c r="G97" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3267,56 +3267,56 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2051</v>
+        <v>2134.35</v>
       </c>
       <c r="E98" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F98" t="n">
-        <v>29.3</v>
+        <v>28.01</v>
       </c>
       <c r="G98" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2046.8</v>
+        <v>2132.8</v>
       </c>
       <c r="E99" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F99" t="n">
-        <v>30.55</v>
+        <v>27.99</v>
       </c>
       <c r="G99" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3325,143 +3325,143 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2037.05</v>
+        <v>2130.55</v>
       </c>
       <c r="E100" t="n">
-        <v>74</v>
+        <v>76.2</v>
       </c>
       <c r="F100" t="n">
-        <v>27.53</v>
+        <v>27.96</v>
       </c>
       <c r="G100" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Zach Edey</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2031.65</v>
+        <v>2129</v>
       </c>
       <c r="E101" t="n">
-        <v>60</v>
+        <v>77.2</v>
       </c>
       <c r="F101" t="n">
-        <v>33.86</v>
+        <v>27.58</v>
       </c>
       <c r="G101" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Day'Ron Sharpe</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2001.15</v>
+        <v>2127.08</v>
       </c>
       <c r="E102" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F102" t="n">
-        <v>30.32</v>
+        <v>27.91</v>
       </c>
       <c r="G102" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1996.25</v>
+        <v>2121.05</v>
       </c>
       <c r="E103" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F103" t="n">
-        <v>27.35</v>
+        <v>27.84</v>
       </c>
       <c r="G103" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1994.3</v>
+        <v>2115.35</v>
       </c>
       <c r="E104" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F104" t="n">
-        <v>31.16</v>
+        <v>27.47</v>
       </c>
       <c r="G104" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3470,85 +3470,85 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1988.25</v>
+        <v>2109.3</v>
       </c>
       <c r="E105" t="n">
-        <v>73</v>
+        <v>77.2</v>
       </c>
       <c r="F105" t="n">
-        <v>27.24</v>
+        <v>27.32</v>
       </c>
       <c r="G105" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Zach LaVine</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1983.65</v>
+        <v>2102.65</v>
       </c>
       <c r="E106" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F106" t="n">
-        <v>29.61</v>
+        <v>27.59</v>
       </c>
       <c r="G106" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1981.7</v>
+        <v>2096.7</v>
       </c>
       <c r="E107" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F107" t="n">
-        <v>29.14</v>
+        <v>27.52</v>
       </c>
       <c r="G107" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3557,71 +3557,71 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1980.15</v>
+        <v>2085.2</v>
       </c>
       <c r="E108" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F108" t="n">
-        <v>29.12</v>
+        <v>36.58</v>
       </c>
       <c r="G108" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kyshawn George</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1957.5</v>
+        <v>2076.4</v>
       </c>
       <c r="E109" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F109" t="n">
-        <v>28.79</v>
+        <v>27.25</v>
       </c>
       <c r="G109" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1955.25</v>
+        <v>2076.05</v>
       </c>
       <c r="E110" t="n">
-        <v>70</v>
+        <v>72.3</v>
       </c>
       <c r="F110" t="n">
-        <v>27.93</v>
+        <v>28.71</v>
       </c>
       <c r="G110" t="n">
         <v>27</v>
@@ -3630,123 +3630,123 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1952.3</v>
+        <v>2070.2</v>
       </c>
       <c r="E111" t="n">
-        <v>71</v>
+        <v>76.2</v>
       </c>
       <c r="F111" t="n">
-        <v>27.5</v>
+        <v>27.17</v>
       </c>
       <c r="G111" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1939.3</v>
+        <v>2067.45</v>
       </c>
       <c r="E112" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F112" t="n">
-        <v>29.84</v>
+        <v>27.13</v>
       </c>
       <c r="G112" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Yaxel Lendeborg</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1933.2</v>
+        <v>2043.25</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>76.2</v>
       </c>
       <c r="F113" t="n">
-        <v>26.12</v>
+        <v>26.81</v>
       </c>
       <c r="G113" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Keegan Murray</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1915.3</v>
+        <v>2034.05</v>
       </c>
       <c r="E114" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="F114" t="n">
-        <v>25.88</v>
+        <v>28.53</v>
       </c>
       <c r="G114" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3756,26 +3756,26 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1914.3</v>
+        <v>2022.9</v>
       </c>
       <c r="E115" t="n">
-        <v>65</v>
+        <v>71.3</v>
       </c>
       <c r="F115" t="n">
-        <v>29.45</v>
+        <v>28.37</v>
       </c>
       <c r="G115" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3785,452 +3785,452 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1914.2</v>
+        <v>2019.25</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>65.5</v>
       </c>
       <c r="F116" t="n">
-        <v>25.52</v>
+        <v>30.83</v>
       </c>
       <c r="G116" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1905.75</v>
+        <v>2018.35</v>
       </c>
       <c r="E117" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F117" t="n">
-        <v>28.44</v>
+        <v>26.49</v>
       </c>
       <c r="G117" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1901.45</v>
+        <v>2002.9</v>
       </c>
       <c r="E118" t="n">
-        <v>68</v>
+        <v>77.2</v>
       </c>
       <c r="F118" t="n">
-        <v>27.96</v>
+        <v>25.94</v>
       </c>
       <c r="G118" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1899.25</v>
+        <v>2000.3</v>
       </c>
       <c r="E119" t="n">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="F119" t="n">
-        <v>27.53</v>
+        <v>26.25</v>
       </c>
       <c r="G119" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Khaman Maluach</t>
+          <t>Zach LaVine</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1896.6</v>
+        <v>1999.2</v>
       </c>
       <c r="E120" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F120" t="n">
-        <v>27.89</v>
+        <v>26.24</v>
       </c>
       <c r="G120" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Ja Morant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1892.25</v>
+        <v>1990.95</v>
       </c>
       <c r="E121" t="n">
-        <v>66</v>
+        <v>77.2</v>
       </c>
       <c r="F121" t="n">
-        <v>28.67</v>
+        <v>25.79</v>
       </c>
       <c r="G121" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1889.35</v>
+        <v>1986.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F122" t="n">
-        <v>25.88</v>
+        <v>26.07</v>
       </c>
       <c r="G122" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mikel Brown Jr.</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1881.6</v>
+        <v>1985.1</v>
       </c>
       <c r="E123" t="n">
-        <v>74</v>
+        <v>75.2</v>
       </c>
       <c r="F123" t="n">
-        <v>25.43</v>
+        <v>26.4</v>
       </c>
       <c r="G123" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1876.95</v>
+        <v>1977.35</v>
       </c>
       <c r="E124" t="n">
-        <v>68</v>
+        <v>77.2</v>
       </c>
       <c r="F124" t="n">
-        <v>27.6</v>
+        <v>25.61</v>
       </c>
       <c r="G124" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1871.9</v>
+        <v>1972.5</v>
       </c>
       <c r="E125" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="F125" t="n">
-        <v>31.2</v>
+        <v>25.89</v>
       </c>
       <c r="G125" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1852.4</v>
+        <v>1961</v>
       </c>
       <c r="E126" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F126" t="n">
-        <v>27.24</v>
+        <v>25.73</v>
       </c>
       <c r="G126" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1848.65</v>
+        <v>1927.85</v>
       </c>
       <c r="E127" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F127" t="n">
-        <v>26.41</v>
+        <v>25.3</v>
       </c>
       <c r="G127" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1840.75</v>
+        <v>1889.55</v>
       </c>
       <c r="E128" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="F128" t="n">
-        <v>24.22</v>
+        <v>24.8</v>
       </c>
       <c r="G128" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1839.35</v>
+        <v>1878.75</v>
       </c>
       <c r="E129" t="n">
-        <v>67</v>
+        <v>77.2</v>
       </c>
       <c r="F129" t="n">
-        <v>27.45</v>
+        <v>24.34</v>
       </c>
       <c r="G129" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1837.75</v>
+        <v>1874.55</v>
       </c>
       <c r="E130" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F130" t="n">
-        <v>28.27</v>
+        <v>24.6</v>
       </c>
       <c r="G130" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1826</v>
+        <v>1873.05</v>
       </c>
       <c r="E131" t="n">
-        <v>72</v>
+        <v>77.2</v>
       </c>
       <c r="F131" t="n">
-        <v>25.36</v>
+        <v>24.26</v>
       </c>
       <c r="G131" t="n">
         <v>22</v>
@@ -4239,12 +4239,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4253,132 +4253,132 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1815.65</v>
+        <v>1849.5</v>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>62.4</v>
       </c>
       <c r="F132" t="n">
-        <v>25.57</v>
+        <v>29.64</v>
       </c>
       <c r="G132" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fred VanVleet</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1814.85</v>
+        <v>1840.55</v>
       </c>
       <c r="E133" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="F133" t="n">
-        <v>30.25</v>
+        <v>24.15</v>
       </c>
       <c r="G133" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Jalen Smith</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1813.7</v>
+        <v>1825.75</v>
       </c>
       <c r="E134" t="n">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="F134" t="n">
-        <v>23.25</v>
+        <v>23.96</v>
       </c>
       <c r="G134" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1807</v>
+        <v>1805.25</v>
       </c>
       <c r="E135" t="n">
-        <v>49</v>
+        <v>77.2</v>
       </c>
       <c r="F135" t="n">
-        <v>36.88</v>
+        <v>23.38</v>
       </c>
       <c r="G135" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1806.55</v>
+        <v>1799.6</v>
       </c>
       <c r="E136" t="n">
-        <v>65</v>
+        <v>77.2</v>
       </c>
       <c r="F136" t="n">
-        <v>27.79</v>
+        <v>23.31</v>
       </c>
       <c r="G136" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137">
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1795.45</v>
+        <v>1795.75</v>
       </c>
       <c r="E137" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="F137" t="n">
-        <v>24.94</v>
+        <v>23.57</v>
       </c>
       <c r="G137" t="n">
         <v>21</v>
@@ -4413,215 +4413,215 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1793.1</v>
+        <v>1788.5</v>
       </c>
       <c r="E138" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F138" t="n">
-        <v>27.59</v>
+        <v>23.47</v>
       </c>
       <c r="G138" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1783.45</v>
+        <v>1785.9</v>
       </c>
       <c r="E139" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F139" t="n">
-        <v>26.23</v>
+        <v>23.44</v>
       </c>
       <c r="G139" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Khaman Maluach</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1778.05</v>
+        <v>1764.25</v>
       </c>
       <c r="E140" t="n">
-        <v>64</v>
+        <v>77.2</v>
       </c>
       <c r="F140" t="n">
-        <v>27.78</v>
+        <v>22.85</v>
       </c>
       <c r="G140" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1749.2</v>
+        <v>1761.45</v>
       </c>
       <c r="E141" t="n">
-        <v>59</v>
+        <v>76.2</v>
       </c>
       <c r="F141" t="n">
-        <v>29.65</v>
+        <v>23.12</v>
       </c>
       <c r="G141" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1745.05</v>
+        <v>1761.3</v>
       </c>
       <c r="E142" t="n">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="F142" t="n">
-        <v>22.37</v>
+        <v>23.11</v>
       </c>
       <c r="G142" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Jaylen Wells</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1736.15</v>
+        <v>1747.6</v>
       </c>
       <c r="E143" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F143" t="n">
-        <v>26.71</v>
+        <v>22.93</v>
       </c>
       <c r="G143" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1731.95</v>
+        <v>1729.65</v>
       </c>
       <c r="E144" t="n">
-        <v>70</v>
+        <v>76.2</v>
       </c>
       <c r="F144" t="n">
-        <v>24.74</v>
+        <v>22.7</v>
       </c>
       <c r="G144" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1729.9</v>
+        <v>1711.5</v>
       </c>
       <c r="E145" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="F145" t="n">
-        <v>28.83</v>
+        <v>22.46</v>
       </c>
       <c r="G145" t="n">
         <v>26</v>
@@ -4645,27 +4645,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Isaiah Stewart</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1725.85</v>
+        <v>1694.1</v>
       </c>
       <c r="E146" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F146" t="n">
-        <v>25.38</v>
+        <v>22.23</v>
       </c>
       <c r="G146" t="n">
         <v>25</v>
@@ -4674,186 +4674,186 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Brayden Burries</t>
+          <t>Bobby Portis Jr.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1723.15</v>
+        <v>1674.38</v>
       </c>
       <c r="E147" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F147" t="n">
-        <v>22.98</v>
+        <v>21.97</v>
       </c>
       <c r="G147" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Keaton Wagler</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1722.85</v>
+        <v>1640.7</v>
       </c>
       <c r="E148" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F148" t="n">
-        <v>22.97</v>
+        <v>21.53</v>
       </c>
       <c r="G148" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1720.55</v>
+        <v>1637.05</v>
       </c>
       <c r="E149" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F149" t="n">
-        <v>25.3</v>
+        <v>21.48</v>
       </c>
       <c r="G149" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1718.5</v>
+        <v>1636.1</v>
       </c>
       <c r="E150" t="n">
-        <v>79</v>
+        <v>76.2</v>
       </c>
       <c r="F150" t="n">
-        <v>21.75</v>
+        <v>21.47</v>
       </c>
       <c r="G150" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1718.4</v>
+        <v>1627.95</v>
       </c>
       <c r="E151" t="n">
-        <v>55</v>
+        <v>76.2</v>
       </c>
       <c r="F151" t="n">
-        <v>31.24</v>
+        <v>21.36</v>
       </c>
       <c r="G151" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711.1</v>
+        <v>1624.15</v>
       </c>
       <c r="E152" t="n">
-        <v>66</v>
+        <v>77.2</v>
       </c>
       <c r="F152" t="n">
-        <v>25.93</v>
+        <v>21.04</v>
       </c>
       <c r="G152" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4862,143 +4862,143 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710.8</v>
+        <v>1612.8</v>
       </c>
       <c r="E153" t="n">
-        <v>62</v>
+        <v>76.2</v>
       </c>
       <c r="F153" t="n">
-        <v>27.59</v>
+        <v>21.17</v>
       </c>
       <c r="G153" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Bobby Portis Jr.</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1708.45</v>
+        <v>1611.75</v>
       </c>
       <c r="E154" t="n">
-        <v>64</v>
+        <v>77.2</v>
       </c>
       <c r="F154" t="n">
-        <v>26.69</v>
+        <v>20.88</v>
       </c>
       <c r="G154" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1701</v>
+        <v>1607.8</v>
       </c>
       <c r="E155" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="F155" t="n">
-        <v>22.38</v>
+        <v>21.1</v>
       </c>
       <c r="G155" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1699.95</v>
+        <v>1597.95</v>
       </c>
       <c r="E156" t="n">
-        <v>65</v>
+        <v>73.3</v>
       </c>
       <c r="F156" t="n">
-        <v>26.15</v>
+        <v>21.8</v>
       </c>
       <c r="G156" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1691.95</v>
+        <v>1591.8</v>
       </c>
       <c r="E157" t="n">
-        <v>74</v>
+        <v>76.2</v>
       </c>
       <c r="F157" t="n">
-        <v>22.86</v>
+        <v>20.89</v>
       </c>
       <c r="G157" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5007,27 +5007,27 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1677.95</v>
+        <v>1591.5</v>
       </c>
       <c r="E158" t="n">
-        <v>68</v>
+        <v>75.2</v>
       </c>
       <c r="F158" t="n">
-        <v>24.68</v>
+        <v>21.16</v>
       </c>
       <c r="G158" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5036,375 +5036,375 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1673.75</v>
+        <v>1579.65</v>
       </c>
       <c r="E159" t="n">
-        <v>63</v>
+        <v>77.2</v>
       </c>
       <c r="F159" t="n">
-        <v>26.57</v>
+        <v>20.46</v>
       </c>
       <c r="G159" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1672.5</v>
+        <v>1560.55</v>
       </c>
       <c r="E160" t="n">
-        <v>67</v>
+        <v>76.2</v>
       </c>
       <c r="F160" t="n">
-        <v>24.96</v>
+        <v>20.48</v>
       </c>
       <c r="G160" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1654.05</v>
+        <v>1557.7</v>
       </c>
       <c r="E161" t="n">
-        <v>55</v>
+        <v>76.2</v>
       </c>
       <c r="F161" t="n">
-        <v>30.07</v>
+        <v>20.44</v>
       </c>
       <c r="G161" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1650.9</v>
+        <v>1556.2</v>
       </c>
       <c r="E162" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
       <c r="F162" t="n">
-        <v>23.58</v>
+        <v>21.23</v>
       </c>
       <c r="G162" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1644.8</v>
+        <v>1547.35</v>
       </c>
       <c r="E163" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F163" t="n">
-        <v>25.3</v>
+        <v>20.31</v>
       </c>
       <c r="G163" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1641.65</v>
+        <v>1529.4</v>
       </c>
       <c r="E164" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F164" t="n">
-        <v>24.14</v>
+        <v>20.07</v>
       </c>
       <c r="G164" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1637.15</v>
+        <v>1522.45</v>
       </c>
       <c r="E165" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F165" t="n">
-        <v>24.08</v>
+        <v>19.98</v>
       </c>
       <c r="G165" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ja Morant</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1609.85</v>
+        <v>1521.95</v>
       </c>
       <c r="E166" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="F166" t="n">
-        <v>26.83</v>
+        <v>19.97</v>
       </c>
       <c r="G166" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>De'Andre Hunter</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1609.4</v>
+        <v>1517.5</v>
       </c>
       <c r="E167" t="n">
-        <v>65</v>
+        <v>76.2</v>
       </c>
       <c r="F167" t="n">
-        <v>24.76</v>
+        <v>19.91</v>
       </c>
       <c r="G167" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1609.05</v>
+        <v>1513.15</v>
       </c>
       <c r="E168" t="n">
-        <v>71</v>
+        <v>76.2</v>
       </c>
       <c r="F168" t="n">
-        <v>22.66</v>
+        <v>19.86</v>
       </c>
       <c r="G168" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1604.9</v>
+        <v>1512.35</v>
       </c>
       <c r="E169" t="n">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="F169" t="n">
-        <v>23.26</v>
+        <v>19.85</v>
       </c>
       <c r="G169" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Anfernee Simons</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1563.05</v>
+        <v>1508.4</v>
       </c>
       <c r="E170" t="n">
-        <v>68</v>
+        <v>76.2</v>
       </c>
       <c r="F170" t="n">
-        <v>22.99</v>
+        <v>19.8</v>
       </c>
       <c r="G170" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Scotty Pippen Jr.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1562.85</v>
+        <v>1492.1</v>
       </c>
       <c r="E171" t="n">
-        <v>73</v>
+        <v>76.2</v>
       </c>
       <c r="F171" t="n">
-        <v>21.41</v>
+        <v>19.58</v>
       </c>
       <c r="G171" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5413,42 +5413,42 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1557.45</v>
+        <v>1491.03</v>
       </c>
       <c r="E172" t="n">
-        <v>71</v>
+        <v>76.2</v>
       </c>
       <c r="F172" t="n">
-        <v>21.94</v>
+        <v>19.57</v>
       </c>
       <c r="G172" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1555.95</v>
+        <v>1484.95</v>
       </c>
       <c r="E173" t="n">
-        <v>71</v>
+        <v>76.2</v>
       </c>
       <c r="F173" t="n">
-        <v>21.91</v>
+        <v>19.49</v>
       </c>
       <c r="G173" t="n">
         <v>27</v>
@@ -5457,41 +5457,41 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1547.25</v>
+        <v>1484.8</v>
       </c>
       <c r="E174" t="n">
-        <v>65</v>
+        <v>59.4</v>
       </c>
       <c r="F174" t="n">
-        <v>23.8</v>
+        <v>25</v>
       </c>
       <c r="G174" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5500,13 +5500,13 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1535.15</v>
+        <v>1476.9</v>
       </c>
       <c r="E175" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="F175" t="n">
-        <v>25.59</v>
+        <v>19.38</v>
       </c>
       <c r="G175" t="n">
         <v>28</v>
@@ -5515,30 +5515,117 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1530.75</v>
+        <v>1467.05</v>
       </c>
       <c r="E176" t="n">
-        <v>66</v>
+        <v>76.2</v>
       </c>
       <c r="F176" t="n">
-        <v>23.19</v>
+        <v>19.25</v>
       </c>
       <c r="G176" t="n">
-        <v>26</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Aaron Wiggins</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SG,SF</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1054.78</v>
+      </c>
+      <c r="E177" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="G177" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Cameron Boozer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Darius Acuff Jr.</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -5575,7 +5662,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>d69e58bfb1be40405868156a38b04733c256e289149d896ce94f04e95ea43ca5</t>
+          <t>ff735f65ff04cfb70b8d6200655b688db8e1765c011cf242e69443f80fcdc54d</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13T16:39:36</t>
+          <t>2026-10-26T17:53:21</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5685,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">

--- a/data/PLAYERLIST.xlsx
+++ b/data/PLAYERLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_fetch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_fetch" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4632.05</v>
+        <v>4630.05</v>
       </c>
       <c r="E2" t="n">
         <v>77.2</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>59.97</v>
       </c>
       <c r="G2" t="n">
         <v>31</v>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4115.2</v>
+        <v>4115.25</v>
       </c>
       <c r="E3" t="n">
         <v>76.2</v>
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3926</v>
+        <v>3924.05</v>
       </c>
       <c r="E4" t="n">
         <v>76.2</v>
       </c>
       <c r="F4" t="n">
-        <v>51.52</v>
+        <v>51.5</v>
       </c>
       <c r="G4" t="n">
         <v>22</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3658.15</v>
+        <v>3644.25</v>
       </c>
       <c r="E5" t="n">
         <v>76.2</v>
       </c>
       <c r="F5" t="n">
-        <v>48.01</v>
+        <v>47.82</v>
       </c>
       <c r="G5" t="n">
         <v>28</v>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3577.8</v>
+        <v>3566.65</v>
       </c>
       <c r="E6" t="n">
         <v>76.2</v>
       </c>
       <c r="F6" t="n">
-        <v>46.95</v>
+        <v>46.81</v>
       </c>
       <c r="G6" t="n">
         <v>24</v>
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3472.25</v>
+        <v>3477.15</v>
       </c>
       <c r="E7" t="n">
         <v>77</v>
       </c>
       <c r="F7" t="n">
-        <v>45.09</v>
+        <v>45.16</v>
       </c>
       <c r="G7" t="n">
         <v>29</v>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3437</v>
+        <v>3440.75</v>
       </c>
       <c r="E8" t="n">
         <v>76.2</v>
       </c>
       <c r="F8" t="n">
-        <v>45.1</v>
+        <v>45.15</v>
       </c>
       <c r="G8" t="n">
         <v>32</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3430.6</v>
+        <v>3430.3</v>
       </c>
       <c r="E9" t="n">
         <v>76.2</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3288.55</v>
+        <v>3288.5</v>
       </c>
       <c r="E10" t="n">
         <v>76.2</v>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3229.55</v>
+        <v>3236.1</v>
       </c>
       <c r="E12" t="n">
         <v>77.2</v>
       </c>
       <c r="F12" t="n">
-        <v>41.83</v>
+        <v>41.92</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3228.5</v>
+        <v>3234.75</v>
       </c>
       <c r="E13" t="n">
         <v>76.2</v>
       </c>
       <c r="F13" t="n">
-        <v>42.37</v>
+        <v>42.45</v>
       </c>
       <c r="G13" t="n">
         <v>26</v>
@@ -846,12 +846,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Josh Giddey</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3109.6</v>
+        <v>3104.95</v>
       </c>
       <c r="E15" t="n">
         <v>76.2</v>
       </c>
       <c r="F15" t="n">
-        <v>40.81</v>
+        <v>40.75</v>
       </c>
       <c r="G15" t="n">
         <v>24</v>
@@ -875,12 +875,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Josh Giddey</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3092.95</v>
+        <v>3096.35</v>
       </c>
       <c r="E16" t="n">
         <v>76.2</v>
       </c>
       <c r="F16" t="n">
-        <v>40.59</v>
+        <v>40.63</v>
       </c>
       <c r="G16" t="n">
         <v>24</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3084.75</v>
+        <v>3080.25</v>
       </c>
       <c r="E18" t="n">
         <v>76.2</v>
       </c>
       <c r="F18" t="n">
-        <v>40.48</v>
+        <v>40.42</v>
       </c>
       <c r="G18" t="n">
         <v>31</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3027.4</v>
+        <v>3046.3</v>
       </c>
       <c r="E19" t="n">
         <v>76.2</v>
       </c>
       <c r="F19" t="n">
-        <v>39.73</v>
+        <v>39.98</v>
       </c>
       <c r="G19" t="n">
         <v>20</v>
@@ -1020,21 +1020,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Alperen Şengün</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2967.05</v>
+        <v>2967.45</v>
       </c>
       <c r="E21" t="n">
         <v>76.2</v>
@@ -1043,36 +1043,36 @@
         <v>38.94</v>
       </c>
       <c r="G21" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alperen Şengün</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2953.4</v>
+        <v>2967.05</v>
       </c>
       <c r="E22" t="n">
         <v>76.2</v>
       </c>
       <c r="F22" t="n">
-        <v>38.76</v>
+        <v>38.94</v>
       </c>
       <c r="G22" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2952.95</v>
+        <v>2952.2</v>
       </c>
       <c r="E23" t="n">
         <v>76.2</v>
       </c>
       <c r="F23" t="n">
-        <v>38.75</v>
+        <v>38.74</v>
       </c>
       <c r="G23" t="n">
         <v>28</v>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2948.4</v>
+        <v>2944.7</v>
       </c>
       <c r="E24" t="n">
         <v>76.2</v>
       </c>
       <c r="F24" t="n">
-        <v>38.69</v>
+        <v>38.64</v>
       </c>
       <c r="G24" t="n">
         <v>28</v>
@@ -1136,12 +1136,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1150,27 +1150,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2941.75</v>
+        <v>2928.05</v>
       </c>
       <c r="E25" t="n">
         <v>77.2</v>
       </c>
       <c r="F25" t="n">
-        <v>38.11</v>
+        <v>37.93</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1179,16 +1179,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2929.9</v>
+        <v>2923.35</v>
       </c>
       <c r="E26" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F26" t="n">
-        <v>37.95</v>
+        <v>38.36</v>
       </c>
       <c r="G26" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2924.15</v>
+        <v>2922.35</v>
       </c>
       <c r="E27" t="n">
         <v>77.2</v>
       </c>
       <c r="F27" t="n">
-        <v>37.88</v>
+        <v>37.85</v>
       </c>
       <c r="G27" t="n">
         <v>25</v>
@@ -1223,175 +1223,175 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2912.2</v>
+        <v>2922.05</v>
       </c>
       <c r="E28" t="n">
         <v>77.2</v>
       </c>
       <c r="F28" t="n">
-        <v>37.72</v>
+        <v>37.85</v>
       </c>
       <c r="G28" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2907</v>
+        <v>2912.2</v>
       </c>
       <c r="E29" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F29" t="n">
-        <v>38.15</v>
+        <v>37.72</v>
       </c>
       <c r="G29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2892.45</v>
+        <v>2882.45</v>
       </c>
       <c r="E30" t="n">
-        <v>65.5</v>
+        <v>76.2</v>
       </c>
       <c r="F30" t="n">
-        <v>44.16</v>
+        <v>37.83</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2890.1</v>
+        <v>2882.05</v>
       </c>
       <c r="E31" t="n">
         <v>76.2</v>
       </c>
       <c r="F31" t="n">
-        <v>37.93</v>
+        <v>37.82</v>
       </c>
       <c r="G31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Lauri Markkanen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2881.6</v>
+        <v>2877.65</v>
       </c>
       <c r="E32" t="n">
         <v>76.2</v>
       </c>
       <c r="F32" t="n">
-        <v>37.82</v>
+        <v>37.76</v>
       </c>
       <c r="G32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lauri Markkanen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2877.65</v>
+        <v>2854.75</v>
       </c>
       <c r="E33" t="n">
-        <v>76.2</v>
+        <v>65.5</v>
       </c>
       <c r="F33" t="n">
-        <v>37.76</v>
+        <v>43.58</v>
       </c>
       <c r="G33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -1455,59 +1455,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2819.95</v>
+        <v>2821.5</v>
       </c>
       <c r="E36" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F36" t="n">
-        <v>37.01</v>
+        <v>36.55</v>
       </c>
       <c r="G36" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2817</v>
+        <v>2819.95</v>
       </c>
       <c r="E37" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F37" t="n">
-        <v>36.49</v>
+        <v>37.01</v>
       </c>
       <c r="G37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
@@ -1542,59 +1542,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Walker Kessler</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2795.2</v>
+        <v>2799.4</v>
       </c>
       <c r="E39" t="n">
         <v>76.2</v>
       </c>
       <c r="F39" t="n">
-        <v>36.68</v>
+        <v>36.74</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Walker Kessler</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2780.45</v>
+        <v>2795.7</v>
       </c>
       <c r="E40" t="n">
         <v>76.2</v>
       </c>
       <c r="F40" t="n">
-        <v>36.49</v>
+        <v>36.69</v>
       </c>
       <c r="G40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2776.4</v>
+        <v>2776.65</v>
       </c>
       <c r="E41" t="n">
         <v>77.2</v>
       </c>
       <c r="F41" t="n">
-        <v>35.96</v>
+        <v>35.97</v>
       </c>
       <c r="G41" t="n">
         <v>25</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2714.95</v>
+        <v>2714.55</v>
       </c>
       <c r="E44" t="n">
         <v>76.2</v>
       </c>
       <c r="F44" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="G44" t="n">
         <v>25</v>
@@ -1745,7 +1745,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1755,26 +1755,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2705.05</v>
+        <v>2709.1</v>
       </c>
       <c r="E46" t="n">
         <v>76.2</v>
       </c>
       <c r="F46" t="n">
-        <v>35.5</v>
+        <v>35.55</v>
       </c>
       <c r="G46" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1784,20 +1784,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2698.4</v>
+        <v>2691.95</v>
       </c>
       <c r="E47" t="n">
         <v>76.2</v>
       </c>
       <c r="F47" t="n">
-        <v>35.41</v>
+        <v>35.33</v>
       </c>
       <c r="G47" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2674.15</v>
+        <v>2674.35</v>
       </c>
       <c r="E48" t="n">
         <v>76.2</v>
       </c>
       <c r="F48" t="n">
-        <v>35.09</v>
+        <v>35.1</v>
       </c>
       <c r="G48" t="n">
         <v>34</v>
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2661.45</v>
+        <v>2653.45</v>
       </c>
       <c r="E49" t="n">
         <v>76.2</v>
       </c>
       <c r="F49" t="n">
-        <v>34.93</v>
+        <v>34.82</v>
       </c>
       <c r="G49" t="n">
         <v>21</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2647.4</v>
+        <v>2647.15</v>
       </c>
       <c r="E51" t="n">
         <v>76.2</v>
@@ -1919,70 +1919,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2628</v>
+        <v>2626.5</v>
       </c>
       <c r="E52" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F52" t="n">
-        <v>34.49</v>
+        <v>34.93</v>
       </c>
       <c r="G52" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2626.5</v>
+        <v>2621.3</v>
       </c>
       <c r="E53" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F53" t="n">
-        <v>34.93</v>
+        <v>34.4</v>
       </c>
       <c r="G53" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Keyonte George</t>
+          <t>Ty Jerome</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1991,27 +1991,27 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2592.7</v>
+        <v>2593.1</v>
       </c>
       <c r="E54" t="n">
         <v>76.2</v>
       </c>
       <c r="F54" t="n">
-        <v>34.02</v>
+        <v>34.03</v>
       </c>
       <c r="G54" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ty Jerome</t>
+          <t>Keyonte George</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2020,103 +2020,103 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2591.1</v>
+        <v>2592.7</v>
       </c>
       <c r="E55" t="n">
         <v>76.2</v>
       </c>
       <c r="F55" t="n">
-        <v>34</v>
+        <v>34.02</v>
       </c>
       <c r="G55" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2560.35</v>
+        <v>2560.9</v>
       </c>
       <c r="E56" t="n">
-        <v>76.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="F56" t="n">
-        <v>33.64</v>
+        <v>33.17</v>
       </c>
       <c r="G56" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2533.95</v>
+        <v>2557.85</v>
       </c>
       <c r="E57" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>33.25</v>
+        <v>33.61</v>
       </c>
       <c r="G57" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2532.65</v>
+        <v>2533.95</v>
       </c>
       <c r="E58" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F58" t="n">
-        <v>32.81</v>
+        <v>33.25</v>
       </c>
       <c r="G58" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
@@ -2151,30 +2151,30 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>N. Alexander-Walker</t>
+          <t>Cameron Boozer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2509.05</v>
+        <v>2527.55</v>
       </c>
       <c r="E60" t="n">
         <v>76.2</v>
       </c>
       <c r="F60" t="n">
-        <v>32.93</v>
+        <v>33.17</v>
       </c>
       <c r="G60" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2499.6</v>
+        <v>2499.15</v>
       </c>
       <c r="E61" t="n">
         <v>76.2</v>
@@ -2209,27 +2209,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>N. Alexander-Walker</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2486.75</v>
+        <v>2492.6</v>
       </c>
       <c r="E62" t="n">
         <v>76.2</v>
       </c>
       <c r="F62" t="n">
-        <v>32.63</v>
+        <v>32.71</v>
       </c>
       <c r="G62" t="n">
         <v>28</v>
@@ -2238,59 +2238,59 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2475.45</v>
+        <v>2483.75</v>
       </c>
       <c r="E63" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F63" t="n">
-        <v>32.92</v>
+        <v>32.6</v>
       </c>
       <c r="G63" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2466.15</v>
+        <v>2475.95</v>
       </c>
       <c r="E64" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F64" t="n">
-        <v>32.36</v>
+        <v>32.92</v>
       </c>
       <c r="G64" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2460.85</v>
+        <v>2460.55</v>
       </c>
       <c r="E65" t="n">
         <v>76.2</v>
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2452.15</v>
+        <v>2451.4</v>
       </c>
       <c r="E66" t="n">
         <v>61.6</v>
       </c>
       <c r="F66" t="n">
-        <v>39.81</v>
+        <v>39.8</v>
       </c>
       <c r="G66" t="n">
         <v>34</v>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2450.1</v>
+        <v>2449.9</v>
       </c>
       <c r="E67" t="n">
         <v>77.2</v>
       </c>
       <c r="F67" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="G67" t="n">
         <v>29</v>
@@ -2383,128 +2383,128 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2446.9</v>
+        <v>2449.5</v>
       </c>
       <c r="E68" t="n">
-        <v>70.3</v>
+        <v>76.2</v>
       </c>
       <c r="F68" t="n">
-        <v>34.81</v>
+        <v>32.15</v>
       </c>
       <c r="G68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2441.2</v>
+        <v>2446.9</v>
       </c>
       <c r="E69" t="n">
-        <v>64.3</v>
+        <v>70.3</v>
       </c>
       <c r="F69" t="n">
-        <v>37.97</v>
+        <v>34.81</v>
       </c>
       <c r="G69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jaren Jackson Jr.</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2356.05</v>
+        <v>2441.2</v>
       </c>
       <c r="E70" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="F70" t="n">
-        <v>30.92</v>
+        <v>37.97</v>
       </c>
       <c r="G70" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Jaren Jackson Jr.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2346.15</v>
+        <v>2356.05</v>
       </c>
       <c r="E71" t="n">
         <v>76.2</v>
       </c>
       <c r="F71" t="n">
-        <v>30.79</v>
+        <v>30.92</v>
       </c>
       <c r="G71" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Darius Acuff Jr.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2345.9</v>
+        <v>2355.34</v>
       </c>
       <c r="E72" t="n">
         <v>76.2</v>
       </c>
       <c r="F72" t="n">
-        <v>30.79</v>
+        <v>30.91</v>
       </c>
       <c r="G72" t="n">
         <v>29</v>
@@ -2528,41 +2528,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2332.75</v>
+        <v>2345.9</v>
       </c>
       <c r="E73" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F73" t="n">
-        <v>30.22</v>
+        <v>30.79</v>
       </c>
       <c r="G73" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ivica Zubac</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2571,56 +2571,56 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2316.95</v>
+        <v>2342.85</v>
       </c>
       <c r="E74" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F74" t="n">
-        <v>30.81</v>
+        <v>30.75</v>
       </c>
       <c r="G74" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2305.05</v>
+        <v>2332.2</v>
       </c>
       <c r="E75" t="n">
-        <v>76.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="F75" t="n">
-        <v>30.29</v>
+        <v>30.21</v>
       </c>
       <c r="G75" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Ivica Zubac</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2629,100 +2629,100 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2305</v>
+        <v>2316.5</v>
       </c>
       <c r="E76" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F76" t="n">
-        <v>30.25</v>
+        <v>30.8</v>
       </c>
       <c r="G76" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2302.1</v>
+        <v>2315.6</v>
       </c>
       <c r="E77" t="n">
         <v>76.2</v>
       </c>
       <c r="F77" t="n">
-        <v>30.21</v>
+        <v>30.39</v>
       </c>
       <c r="G77" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Day'Ron Sharpe</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2298.45</v>
+        <v>2314.6</v>
       </c>
       <c r="E78" t="n">
         <v>76.2</v>
       </c>
       <c r="F78" t="n">
-        <v>30.16</v>
+        <v>30.38</v>
       </c>
       <c r="G78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2285.92</v>
+        <v>2304.5</v>
       </c>
       <c r="E79" t="n">
-        <v>77.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>29.61</v>
+        <v>30.28</v>
       </c>
       <c r="G79" t="n">
         <v>29</v>
@@ -2731,233 +2731,233 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fred VanVleet</t>
+          <t>Day'Ron Sharpe</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2252.15</v>
+        <v>2301.45</v>
       </c>
       <c r="E80" t="n">
         <v>76.2</v>
       </c>
       <c r="F80" t="n">
-        <v>29.56</v>
+        <v>30.2</v>
       </c>
       <c r="G80" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2226.8</v>
+        <v>2277.32</v>
       </c>
       <c r="E81" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F81" t="n">
-        <v>29.22</v>
+        <v>29.5</v>
       </c>
       <c r="G81" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Fred VanVleet</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2226</v>
+        <v>2235.7</v>
       </c>
       <c r="E82" t="n">
         <v>76.2</v>
       </c>
       <c r="F82" t="n">
-        <v>29.21</v>
+        <v>29.34</v>
       </c>
       <c r="G82" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Egor Dëmin</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2214.15</v>
+        <v>2234.75</v>
       </c>
       <c r="E83" t="n">
         <v>76.2</v>
       </c>
       <c r="F83" t="n">
-        <v>29.06</v>
+        <v>29.33</v>
       </c>
       <c r="G83" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2207.25</v>
+        <v>2223.9</v>
       </c>
       <c r="E84" t="n">
         <v>76.2</v>
       </c>
       <c r="F84" t="n">
-        <v>28.97</v>
+        <v>29.19</v>
       </c>
       <c r="G84" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Egor Dëmin</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2205.35</v>
+        <v>2214.15</v>
       </c>
       <c r="E85" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F85" t="n">
-        <v>28.57</v>
+        <v>29.06</v>
       </c>
       <c r="G85" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zach Edey</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2198.7</v>
+        <v>2207.25</v>
       </c>
       <c r="E86" t="n">
         <v>76.2</v>
       </c>
       <c r="F86" t="n">
-        <v>28.85</v>
+        <v>28.97</v>
       </c>
       <c r="G86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2197.8</v>
+        <v>2205.8</v>
       </c>
       <c r="E87" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F87" t="n">
-        <v>28.84</v>
+        <v>28.57</v>
       </c>
       <c r="G87" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2195.85</v>
+        <v>2198.95</v>
       </c>
       <c r="E88" t="n">
         <v>77.2</v>
       </c>
       <c r="F88" t="n">
-        <v>28.44</v>
+        <v>28.48</v>
       </c>
       <c r="G88" t="n">
         <v>28</v>
@@ -2992,12 +2992,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jusuf Nurkić</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3006,114 +3006,114 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2193.3</v>
+        <v>2198.7</v>
       </c>
       <c r="E89" t="n">
-        <v>72.3</v>
+        <v>76.2</v>
       </c>
       <c r="F89" t="n">
-        <v>30.34</v>
+        <v>28.85</v>
       </c>
       <c r="G89" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2189.85</v>
+        <v>2194.15</v>
       </c>
       <c r="E90" t="n">
-        <v>70.3</v>
+        <v>76.2</v>
       </c>
       <c r="F90" t="n">
-        <v>31.15</v>
+        <v>28.79</v>
       </c>
       <c r="G90" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Jusuf Nurkić</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2186.1</v>
+        <v>2193.3</v>
       </c>
       <c r="E91" t="n">
-        <v>73.3</v>
+        <v>72.3</v>
       </c>
       <c r="F91" t="n">
-        <v>29.82</v>
+        <v>30.34</v>
       </c>
       <c r="G91" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2172.35</v>
+        <v>2189.85</v>
       </c>
       <c r="E92" t="n">
-        <v>76.2</v>
+        <v>70.3</v>
       </c>
       <c r="F92" t="n">
-        <v>28.51</v>
+        <v>31.15</v>
       </c>
       <c r="G92" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3122,56 +3122,56 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2168.9</v>
+        <v>2186.1</v>
       </c>
       <c r="E93" t="n">
-        <v>76.2</v>
+        <v>73.3</v>
       </c>
       <c r="F93" t="n">
-        <v>28.46</v>
+        <v>29.82</v>
       </c>
       <c r="G93" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2165.4</v>
+        <v>2174.7</v>
       </c>
       <c r="E94" t="n">
         <v>76.2</v>
       </c>
       <c r="F94" t="n">
-        <v>28.42</v>
+        <v>28.54</v>
       </c>
       <c r="G94" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3180,56 +3180,56 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2150.9</v>
+        <v>2165.4</v>
       </c>
       <c r="E95" t="n">
         <v>76.2</v>
       </c>
       <c r="F95" t="n">
-        <v>28.23</v>
+        <v>28.42</v>
       </c>
       <c r="G95" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2142.35</v>
+        <v>2161.98</v>
       </c>
       <c r="E96" t="n">
         <v>76.2</v>
       </c>
       <c r="F96" t="n">
-        <v>28.11</v>
+        <v>28.37</v>
       </c>
       <c r="G96" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3238,74 +3238,74 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2138.3</v>
+        <v>2141.6</v>
       </c>
       <c r="E97" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F97" t="n">
-        <v>28.43</v>
+        <v>28.1</v>
       </c>
       <c r="G97" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2134.35</v>
+        <v>2138.3</v>
       </c>
       <c r="E98" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F98" t="n">
-        <v>28.01</v>
+        <v>28.43</v>
       </c>
       <c r="G98" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2132.8</v>
+        <v>2137.65</v>
       </c>
       <c r="E99" t="n">
         <v>76.2</v>
       </c>
       <c r="F99" t="n">
-        <v>27.99</v>
+        <v>28.05</v>
       </c>
       <c r="G99" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2129</v>
+        <v>2128.55</v>
       </c>
       <c r="E101" t="n">
         <v>77.2</v>
       </c>
       <c r="F101" t="n">
-        <v>27.58</v>
+        <v>27.57</v>
       </c>
       <c r="G101" t="n">
         <v>25</v>
@@ -3398,12 +3398,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3412,27 +3412,27 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2121.05</v>
+        <v>2126.85</v>
       </c>
       <c r="E103" t="n">
         <v>76.2</v>
       </c>
       <c r="F103" t="n">
-        <v>27.84</v>
+        <v>27.91</v>
       </c>
       <c r="G103" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3441,56 +3441,56 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2115.35</v>
+        <v>2125</v>
       </c>
       <c r="E104" t="n">
-        <v>77</v>
+        <v>76.2</v>
       </c>
       <c r="F104" t="n">
-        <v>27.47</v>
+        <v>27.89</v>
       </c>
       <c r="G104" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2109.3</v>
+        <v>2121.8</v>
       </c>
       <c r="E105" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F105" t="n">
-        <v>27.32</v>
+        <v>27.85</v>
       </c>
       <c r="G105" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3499,27 +3499,27 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2102.65</v>
+        <v>2118.67</v>
       </c>
       <c r="E106" t="n">
         <v>76.2</v>
       </c>
       <c r="F106" t="n">
-        <v>27.59</v>
+        <v>27.8</v>
       </c>
       <c r="G106" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3528,71 +3528,71 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2096.7</v>
+        <v>2116.7</v>
       </c>
       <c r="E107" t="n">
         <v>76.2</v>
       </c>
       <c r="F107" t="n">
-        <v>27.52</v>
+        <v>27.78</v>
       </c>
       <c r="G107" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2085.2</v>
+        <v>2115.35</v>
       </c>
       <c r="E108" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F108" t="n">
-        <v>36.58</v>
+        <v>27.47</v>
       </c>
       <c r="G108" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2076.4</v>
+        <v>2109.3</v>
       </c>
       <c r="E109" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F109" t="n">
-        <v>27.25</v>
+        <v>27.32</v>
       </c>
       <c r="G109" t="n">
         <v>36</v>
@@ -3601,12 +3601,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3615,71 +3615,71 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2076.05</v>
+        <v>2085.7</v>
       </c>
       <c r="E110" t="n">
-        <v>72.3</v>
+        <v>57</v>
       </c>
       <c r="F110" t="n">
-        <v>28.71</v>
+        <v>36.59</v>
       </c>
       <c r="G110" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2070.2</v>
+        <v>2076.4</v>
       </c>
       <c r="E111" t="n">
         <v>76.2</v>
       </c>
       <c r="F111" t="n">
-        <v>27.17</v>
+        <v>27.25</v>
       </c>
       <c r="G111" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2067.45</v>
+        <v>2076.05</v>
       </c>
       <c r="E112" t="n">
-        <v>76.2</v>
+        <v>72.3</v>
       </c>
       <c r="F112" t="n">
-        <v>27.13</v>
+        <v>28.71</v>
       </c>
       <c r="G112" t="n">
         <v>27</v>
@@ -3688,114 +3688,114 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2043.25</v>
+        <v>2070.2</v>
       </c>
       <c r="E113" t="n">
         <v>76.2</v>
       </c>
       <c r="F113" t="n">
-        <v>26.81</v>
+        <v>27.17</v>
       </c>
       <c r="G113" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Keegan Murray</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2034.05</v>
+        <v>2051.6</v>
       </c>
       <c r="E114" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
       <c r="F114" t="n">
-        <v>28.53</v>
+        <v>26.92</v>
       </c>
       <c r="G114" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2022.9</v>
+        <v>2043.5</v>
       </c>
       <c r="E115" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
       <c r="F115" t="n">
-        <v>28.37</v>
+        <v>26.82</v>
       </c>
       <c r="G115" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Keegan Murray</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2019.25</v>
+        <v>2034.05</v>
       </c>
       <c r="E116" t="n">
-        <v>65.5</v>
+        <v>71.3</v>
       </c>
       <c r="F116" t="n">
-        <v>30.83</v>
+        <v>28.53</v>
       </c>
       <c r="G116" t="n">
         <v>26</v>
@@ -3818,13 +3818,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2018.35</v>
+        <v>2032.35</v>
       </c>
       <c r="E117" t="n">
         <v>76.2</v>
       </c>
       <c r="F117" t="n">
-        <v>26.49</v>
+        <v>26.67</v>
       </c>
       <c r="G117" t="n">
         <v>22</v>
@@ -3833,41 +3833,41 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2002.9</v>
+        <v>2022.9</v>
       </c>
       <c r="E118" t="n">
-        <v>77.2</v>
+        <v>71.3</v>
       </c>
       <c r="F118" t="n">
-        <v>25.94</v>
+        <v>28.37</v>
       </c>
       <c r="G118" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3876,370 +3876,370 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2000.3</v>
+        <v>2019.25</v>
       </c>
       <c r="E119" t="n">
-        <v>76.2</v>
+        <v>65.5</v>
       </c>
       <c r="F119" t="n">
-        <v>26.25</v>
+        <v>30.83</v>
       </c>
       <c r="G119" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Zach LaVine</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1999.2</v>
+        <v>2012.5</v>
       </c>
       <c r="E120" t="n">
         <v>76.2</v>
       </c>
       <c r="F120" t="n">
-        <v>26.24</v>
+        <v>26.41</v>
       </c>
       <c r="G120" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ja Morant</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1990.95</v>
+        <v>2009.35</v>
       </c>
       <c r="E121" t="n">
         <v>77.2</v>
       </c>
       <c r="F121" t="n">
-        <v>25.79</v>
+        <v>26.03</v>
       </c>
       <c r="G121" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Zach LaVine</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1986.3</v>
+        <v>1999.65</v>
       </c>
       <c r="E122" t="n">
         <v>76.2</v>
       </c>
       <c r="F122" t="n">
-        <v>26.07</v>
+        <v>26.24</v>
       </c>
       <c r="G122" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1985.1</v>
+        <v>1993.7</v>
       </c>
       <c r="E123" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F123" t="n">
-        <v>26.4</v>
+        <v>26.16</v>
       </c>
       <c r="G123" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Ja Morant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1977.35</v>
+        <v>1990.95</v>
       </c>
       <c r="E124" t="n">
         <v>77.2</v>
       </c>
       <c r="F124" t="n">
-        <v>25.61</v>
+        <v>25.79</v>
       </c>
       <c r="G124" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1972.5</v>
+        <v>1985.45</v>
       </c>
       <c r="E125" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F125" t="n">
-        <v>25.89</v>
+        <v>26.4</v>
       </c>
       <c r="G125" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1961</v>
+        <v>1977.35</v>
       </c>
       <c r="E126" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F126" t="n">
-        <v>25.73</v>
+        <v>25.61</v>
       </c>
       <c r="G126" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1927.85</v>
+        <v>1972.5</v>
       </c>
       <c r="E127" t="n">
         <v>76.2</v>
       </c>
       <c r="F127" t="n">
-        <v>25.3</v>
+        <v>25.89</v>
       </c>
       <c r="G127" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1889.55</v>
+        <v>1964</v>
       </c>
       <c r="E128" t="n">
         <v>76.2</v>
       </c>
       <c r="F128" t="n">
-        <v>24.8</v>
+        <v>25.77</v>
       </c>
       <c r="G128" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1878.75</v>
+        <v>1927.85</v>
       </c>
       <c r="E129" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F129" t="n">
-        <v>24.34</v>
+        <v>25.3</v>
       </c>
       <c r="G129" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1874.55</v>
+        <v>1889.55</v>
       </c>
       <c r="E130" t="n">
         <v>76.2</v>
       </c>
       <c r="F130" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="G130" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1873.05</v>
+        <v>1874.55</v>
       </c>
       <c r="E131" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F131" t="n">
-        <v>24.26</v>
+        <v>24.6</v>
       </c>
       <c r="G131" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4249,307 +4249,307 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1849.5</v>
+        <v>1873.95</v>
       </c>
       <c r="E132" t="n">
-        <v>62.4</v>
+        <v>77.2</v>
       </c>
       <c r="F132" t="n">
-        <v>29.64</v>
+        <v>24.27</v>
       </c>
       <c r="G132" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1840.55</v>
+        <v>1873.05</v>
       </c>
       <c r="E133" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F133" t="n">
-        <v>24.15</v>
+        <v>24.26</v>
       </c>
       <c r="G133" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Jalen Smith</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1825.75</v>
+        <v>1842.15</v>
       </c>
       <c r="E134" t="n">
-        <v>76.2</v>
+        <v>62.4</v>
       </c>
       <c r="F134" t="n">
-        <v>23.96</v>
+        <v>29.52</v>
       </c>
       <c r="G134" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1805.25</v>
+        <v>1827.15</v>
       </c>
       <c r="E135" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F135" t="n">
-        <v>23.38</v>
+        <v>23.98</v>
       </c>
       <c r="G135" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1799.6</v>
+        <v>1823</v>
       </c>
       <c r="E136" t="n">
         <v>77.2</v>
       </c>
       <c r="F136" t="n">
-        <v>23.31</v>
+        <v>23.61</v>
       </c>
       <c r="G136" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Jalen Smith</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1795.75</v>
+        <v>1816.9</v>
       </c>
       <c r="E137" t="n">
         <v>76.2</v>
       </c>
       <c r="F137" t="n">
-        <v>23.57</v>
+        <v>23.84</v>
       </c>
       <c r="G137" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1788.5</v>
+        <v>1800.15</v>
       </c>
       <c r="E138" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F138" t="n">
-        <v>23.47</v>
+        <v>23.32</v>
       </c>
       <c r="G138" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1785.9</v>
+        <v>1795.75</v>
       </c>
       <c r="E139" t="n">
         <v>76.2</v>
       </c>
       <c r="F139" t="n">
-        <v>23.44</v>
+        <v>23.57</v>
       </c>
       <c r="G139" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Khaman Maluach</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1764.25</v>
+        <v>1791.35</v>
       </c>
       <c r="E140" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F140" t="n">
-        <v>22.85</v>
+        <v>23.51</v>
       </c>
       <c r="G140" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1761.45</v>
+        <v>1781.3</v>
       </c>
       <c r="E141" t="n">
         <v>76.2</v>
       </c>
       <c r="F141" t="n">
-        <v>23.12</v>
+        <v>23.38</v>
       </c>
       <c r="G141" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1761.3</v>
+        <v>1768.2</v>
       </c>
       <c r="E142" t="n">
         <v>76.2</v>
       </c>
       <c r="F142" t="n">
-        <v>23.11</v>
+        <v>23.2</v>
       </c>
       <c r="G142" t="n">
         <v>28</v>
@@ -4558,12 +4558,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jaylen Wells</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4572,312 +4572,312 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1747.6</v>
+        <v>1761.3</v>
       </c>
       <c r="E143" t="n">
         <v>76.2</v>
       </c>
       <c r="F143" t="n">
-        <v>22.93</v>
+        <v>23.11</v>
       </c>
       <c r="G143" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Khaman Maluach</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1729.65</v>
+        <v>1754.5</v>
       </c>
       <c r="E144" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F144" t="n">
-        <v>22.7</v>
+        <v>22.73</v>
       </c>
       <c r="G144" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Jaylen Wells</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711.5</v>
+        <v>1747.6</v>
       </c>
       <c r="E145" t="n">
         <v>76.2</v>
       </c>
       <c r="F145" t="n">
-        <v>22.46</v>
+        <v>22.93</v>
       </c>
       <c r="G145" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1694.1</v>
+        <v>1729.65</v>
       </c>
       <c r="E146" t="n">
         <v>76.2</v>
       </c>
       <c r="F146" t="n">
-        <v>22.23</v>
+        <v>22.7</v>
       </c>
       <c r="G146" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Bobby Portis Jr.</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1674.38</v>
+        <v>1711.5</v>
       </c>
       <c r="E147" t="n">
         <v>76.2</v>
       </c>
       <c r="F147" t="n">
-        <v>21.97</v>
+        <v>22.46</v>
       </c>
       <c r="G147" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1640.7</v>
+        <v>1693.1</v>
       </c>
       <c r="E148" t="n">
         <v>76.2</v>
       </c>
       <c r="F148" t="n">
-        <v>21.53</v>
+        <v>22.22</v>
       </c>
       <c r="G148" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Bobby Portis Jr.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1637.05</v>
+        <v>1679.35</v>
       </c>
       <c r="E149" t="n">
         <v>76.2</v>
       </c>
       <c r="F149" t="n">
-        <v>21.48</v>
+        <v>22.04</v>
       </c>
       <c r="G149" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1636.1</v>
+        <v>1640.45</v>
       </c>
       <c r="E150" t="n">
         <v>76.2</v>
       </c>
       <c r="F150" t="n">
-        <v>21.47</v>
+        <v>21.53</v>
       </c>
       <c r="G150" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Kyle Filipowski</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1627.95</v>
+        <v>1636.1</v>
       </c>
       <c r="E151" t="n">
         <v>76.2</v>
       </c>
       <c r="F151" t="n">
-        <v>21.36</v>
+        <v>21.47</v>
       </c>
       <c r="G151" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1624.15</v>
+        <v>1628.45</v>
       </c>
       <c r="E152" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F152" t="n">
-        <v>21.04</v>
+        <v>21.37</v>
       </c>
       <c r="G152" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1612.8</v>
+        <v>1627.1</v>
       </c>
       <c r="E153" t="n">
         <v>76.2</v>
       </c>
       <c r="F153" t="n">
-        <v>21.17</v>
+        <v>21.35</v>
       </c>
       <c r="G153" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4887,118 +4887,118 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1611.75</v>
+        <v>1614.65</v>
       </c>
       <c r="E154" t="n">
         <v>77.2</v>
       </c>
       <c r="F154" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="G154" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1607.8</v>
+        <v>1613.1</v>
       </c>
       <c r="E155" t="n">
         <v>76.2</v>
       </c>
       <c r="F155" t="n">
-        <v>21.1</v>
+        <v>21.17</v>
       </c>
       <c r="G155" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1597.95</v>
+        <v>1612.3</v>
       </c>
       <c r="E156" t="n">
-        <v>73.3</v>
+        <v>77.2</v>
       </c>
       <c r="F156" t="n">
-        <v>21.8</v>
+        <v>20.88</v>
       </c>
       <c r="G156" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1591.8</v>
+        <v>1607.8</v>
       </c>
       <c r="E157" t="n">
         <v>76.2</v>
       </c>
       <c r="F157" t="n">
-        <v>20.89</v>
+        <v>21.1</v>
       </c>
       <c r="G157" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5007,114 +5007,114 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1591.5</v>
+        <v>1597.95</v>
       </c>
       <c r="E158" t="n">
-        <v>75.2</v>
+        <v>73.3</v>
       </c>
       <c r="F158" t="n">
-        <v>21.16</v>
+        <v>21.8</v>
       </c>
       <c r="G158" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1579.65</v>
+        <v>1591.8</v>
       </c>
       <c r="E159" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F159" t="n">
-        <v>20.46</v>
+        <v>20.89</v>
       </c>
       <c r="G159" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1560.55</v>
+        <v>1591.5</v>
       </c>
       <c r="E160" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F160" t="n">
-        <v>20.48</v>
+        <v>21.16</v>
       </c>
       <c r="G160" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1557.7</v>
+        <v>1579.65</v>
       </c>
       <c r="E161" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F161" t="n">
-        <v>20.44</v>
+        <v>20.46</v>
       </c>
       <c r="G161" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5123,85 +5123,85 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1556.2</v>
+        <v>1560.55</v>
       </c>
       <c r="E162" t="n">
-        <v>73.3</v>
+        <v>76.2</v>
       </c>
       <c r="F162" t="n">
-        <v>21.23</v>
+        <v>20.48</v>
       </c>
       <c r="G162" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1547.35</v>
+        <v>1557.85</v>
       </c>
       <c r="E163" t="n">
         <v>76.2</v>
       </c>
       <c r="F163" t="n">
-        <v>20.31</v>
+        <v>20.44</v>
       </c>
       <c r="G163" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1529.4</v>
+        <v>1556.2</v>
       </c>
       <c r="E164" t="n">
-        <v>76.2</v>
+        <v>73.3</v>
       </c>
       <c r="F164" t="n">
-        <v>20.07</v>
+        <v>21.23</v>
       </c>
       <c r="G164" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5210,114 +5210,114 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1522.45</v>
+        <v>1551.05</v>
       </c>
       <c r="E165" t="n">
         <v>76.2</v>
       </c>
       <c r="F165" t="n">
-        <v>19.98</v>
+        <v>20.35</v>
       </c>
       <c r="G165" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1521.95</v>
+        <v>1529.55</v>
       </c>
       <c r="E166" t="n">
         <v>76.2</v>
       </c>
       <c r="F166" t="n">
-        <v>19.97</v>
+        <v>20.07</v>
       </c>
       <c r="G166" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>De'Andre Hunter</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1517.5</v>
+        <v>1526.65</v>
       </c>
       <c r="E167" t="n">
         <v>76.2</v>
       </c>
       <c r="F167" t="n">
-        <v>19.91</v>
+        <v>20.03</v>
       </c>
       <c r="G167" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1513.15</v>
+        <v>1521.95</v>
       </c>
       <c r="E168" t="n">
         <v>76.2</v>
       </c>
       <c r="F168" t="n">
-        <v>19.86</v>
+        <v>19.97</v>
       </c>
       <c r="G168" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>De'Andre Hunter</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1512.35</v>
+        <v>1517.5</v>
       </c>
       <c r="E169" t="n">
         <v>76.2</v>
       </c>
       <c r="F169" t="n">
-        <v>19.85</v>
+        <v>19.91</v>
       </c>
       <c r="G169" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Kyshawn George</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1508.4</v>
+        <v>1511.8</v>
       </c>
       <c r="E170" t="n">
         <v>76.2</v>
       </c>
       <c r="F170" t="n">
-        <v>19.8</v>
+        <v>19.84</v>
       </c>
       <c r="G170" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Scotty Pippen Jr.</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1492.1</v>
+        <v>1509.95</v>
       </c>
       <c r="E171" t="n">
         <v>76.2</v>
       </c>
       <c r="F171" t="n">
-        <v>19.58</v>
+        <v>19.82</v>
       </c>
       <c r="G171" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5413,158 +5413,158 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1491.03</v>
+        <v>1503.7</v>
       </c>
       <c r="E172" t="n">
         <v>76.2</v>
       </c>
       <c r="F172" t="n">
-        <v>19.57</v>
+        <v>19.73</v>
       </c>
       <c r="G172" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Scotty Pippen Jr.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1484.95</v>
+        <v>1492.1</v>
       </c>
       <c r="E173" t="n">
         <v>76.2</v>
       </c>
       <c r="F173" t="n">
-        <v>19.49</v>
+        <v>19.58</v>
       </c>
       <c r="G173" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1484.8</v>
+        <v>1490.58</v>
       </c>
       <c r="E174" t="n">
-        <v>59.4</v>
+        <v>76.2</v>
       </c>
       <c r="F174" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="G174" t="n">
         <v>25</v>
-      </c>
-      <c r="G174" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Kristaps Porziņģis</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1476.9</v>
+        <v>1484.8</v>
       </c>
       <c r="E175" t="n">
-        <v>76.2</v>
+        <v>59.4</v>
       </c>
       <c r="F175" t="n">
-        <v>19.38</v>
+        <v>25</v>
       </c>
       <c r="G175" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1467.05</v>
+        <v>1484.8</v>
       </c>
       <c r="E176" t="n">
         <v>76.2</v>
       </c>
       <c r="F176" t="n">
-        <v>19.25</v>
+        <v>19.49</v>
       </c>
       <c r="G176" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Malik Monk</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1054.78</v>
+        <v>1476.9</v>
       </c>
       <c r="E177" t="n">
         <v>76.2</v>
       </c>
       <c r="F177" t="n">
-        <v>13.84</v>
+        <v>19.38</v>
       </c>
       <c r="G177" t="n">
         <v>28</v>
@@ -5573,59 +5573,59 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Cameron Boozer</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1467.05</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="G178" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Darius Acuff Jr.</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>1056.7</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>13.87</v>
       </c>
       <c r="G179" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5639,7 +5639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ff735f65ff04cfb70b8d6200655b688db8e1765c011cf242e69443f80fcdc54d</t>
+          <t>90a77af709458880df7c2613a030ae4c3020e840c4eb3748457579938ccde3ed</t>
         </is>
       </c>
     </row>
@@ -5674,27 +5674,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T17:53:21</t>
+          <t>2026-10-26T22:09:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>178</v>
+          <t>overrides</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{"applied": [{"now": {"player_proj_GP": 76.2, "player_total_proj_FP": 2527.55, "projectedFPPG": 33.17}, "player_name": "Cameron Boozer", "reason": "Yahoo's rest-of-season view (S_PSR) reports 0 GP / 0.00 FP for a healthy rostered player (Benton)", "replaces": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0}, "replaces_matches": true, "review_by": "2026-11-03", "yahoo": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0, "projectedFPPG": 0.0}, "yahoo_id": "10592"}, {"now": {"player_proj_GP": 76.2, "player_total_proj_FP": 2355.34, "projectedFPPG": 30.91}, "player_name": "Darius Acuff Jr.", "reason": "Yahoo's rest-of-season view (S_PSR) reports 0 GP / 0.00 FP for a healthy rostered player (Hayden)", "replaces": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0}, "replaces_matches": true, "review_by": "2026-11-03", "yahoo": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0, "projectedFPPG": 0.0}, "yahoo_id": "10582"}], "unapplied": []}</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>yahoo:16778</t>
         </is>

--- a/data/PLAYERLIST.xlsx
+++ b/data/PLAYERLIST.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4630.05</v>
+        <v>4570.85</v>
       </c>
       <c r="E2" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F2" t="n">
-        <v>59.97</v>
+        <v>59.98</v>
       </c>
       <c r="G2" t="n">
         <v>31</v>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4115.25</v>
+        <v>4112.75</v>
       </c>
       <c r="E3" t="n">
         <v>76.2</v>
       </c>
       <c r="F3" t="n">
-        <v>54.01</v>
+        <v>53.97</v>
       </c>
       <c r="G3" t="n">
         <v>27</v>
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3924.05</v>
+        <v>3926.05</v>
       </c>
       <c r="E4" t="n">
         <v>76.2</v>
       </c>
       <c r="F4" t="n">
-        <v>51.5</v>
+        <v>51.52</v>
       </c>
       <c r="G4" t="n">
         <v>22</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3644.25</v>
+        <v>3603.5</v>
       </c>
       <c r="E5" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F5" t="n">
-        <v>47.82</v>
+        <v>47.92</v>
       </c>
       <c r="G5" t="n">
         <v>28</v>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3566.65</v>
+        <v>3522.95</v>
       </c>
       <c r="E6" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F6" t="n">
-        <v>46.81</v>
+        <v>46.85</v>
       </c>
       <c r="G6" t="n">
         <v>24</v>
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3477.15</v>
+        <v>3428.5</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>45.16</v>
+        <v>45.05</v>
       </c>
       <c r="G7" t="n">
         <v>29</v>
@@ -643,59 +643,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Giannis Antetokounmpo</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3440.75</v>
+        <v>3424.85</v>
       </c>
       <c r="E8" t="n">
         <v>76.2</v>
       </c>
       <c r="F8" t="n">
-        <v>45.15</v>
+        <v>44.95</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Giannis Antetokounmpo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3430.3</v>
+        <v>3396.1</v>
       </c>
       <c r="E9" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F9" t="n">
-        <v>45.02</v>
+        <v>45.16</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3288.5</v>
+        <v>3287</v>
       </c>
       <c r="E10" t="n">
         <v>76.2</v>
       </c>
       <c r="F10" t="n">
-        <v>43.16</v>
+        <v>43.14</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -730,70 +730,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stephen Curry</t>
+          <t>Tyrese Haliburton</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3245.55</v>
+        <v>3213.8</v>
       </c>
       <c r="E11" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F11" t="n">
-        <v>42.59</v>
+        <v>42.74</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3236.1</v>
+        <v>3209.35</v>
       </c>
       <c r="E12" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F12" t="n">
-        <v>41.92</v>
+        <v>42.68</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tyrese Haliburton</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3234.75</v>
+        <v>3192.9</v>
       </c>
       <c r="E13" t="n">
         <v>76.2</v>
       </c>
       <c r="F13" t="n">
-        <v>42.45</v>
+        <v>41.9</v>
       </c>
       <c r="G13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3205.6</v>
+        <v>3173.45</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>41.63</v>
+        <v>41.7</v>
       </c>
       <c r="G14" t="n">
         <v>29</v>
@@ -846,30 +846,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3104.95</v>
+        <v>3083.7</v>
       </c>
       <c r="E15" t="n">
         <v>76.2</v>
       </c>
       <c r="F15" t="n">
-        <v>40.75</v>
+        <v>40.47</v>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3096.35</v>
+        <v>3065.15</v>
       </c>
       <c r="E16" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F16" t="n">
-        <v>40.63</v>
+        <v>40.76</v>
       </c>
       <c r="G16" t="n">
         <v>24</v>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3086.2</v>
+        <v>3035.35</v>
       </c>
       <c r="E17" t="n">
-        <v>75.2</v>
+        <v>74.2</v>
       </c>
       <c r="F17" t="n">
-        <v>41.04</v>
+        <v>40.91</v>
       </c>
       <c r="G17" t="n">
         <v>24</v>
@@ -933,215 +933,215 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3080.25</v>
+        <v>3021.2</v>
       </c>
       <c r="E18" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F18" t="n">
-        <v>40.42</v>
+        <v>40.18</v>
       </c>
       <c r="G18" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3046.3</v>
+        <v>3000</v>
       </c>
       <c r="E19" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F19" t="n">
-        <v>39.98</v>
+        <v>39.89</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2993.15</v>
+        <v>2952.95</v>
       </c>
       <c r="E20" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F20" t="n">
-        <v>39.8</v>
+        <v>38.75</v>
       </c>
       <c r="G20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alperen Şengün</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2967.45</v>
+        <v>2910.4</v>
       </c>
       <c r="E21" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F21" t="n">
-        <v>38.94</v>
+        <v>37.7</v>
       </c>
       <c r="G21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Trae Young</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2967.05</v>
+        <v>2906.8</v>
       </c>
       <c r="E22" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F22" t="n">
-        <v>38.94</v>
+        <v>38.65</v>
       </c>
       <c r="G22" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2952.2</v>
+        <v>2893.5</v>
       </c>
       <c r="E23" t="n">
         <v>76.2</v>
       </c>
       <c r="F23" t="n">
-        <v>38.74</v>
+        <v>37.97</v>
       </c>
       <c r="G23" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Trae Young</t>
+          <t>Alperen Şengün</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2944.7</v>
+        <v>2891.3</v>
       </c>
       <c r="E24" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="F24" t="n">
-        <v>38.64</v>
+        <v>38.97</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2928.05</v>
+        <v>2887.4</v>
       </c>
       <c r="E25" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F25" t="n">
-        <v>37.93</v>
+        <v>37.89</v>
       </c>
       <c r="G25" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2923.35</v>
+        <v>2886.4</v>
       </c>
       <c r="E26" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F26" t="n">
-        <v>38.36</v>
+        <v>38.38</v>
       </c>
       <c r="G26" t="n">
         <v>27</v>
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2922.35</v>
+        <v>2884.9</v>
       </c>
       <c r="E27" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F27" t="n">
-        <v>37.85</v>
+        <v>37.86</v>
       </c>
       <c r="G27" t="n">
         <v>25</v>
@@ -1223,27 +1223,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2922.05</v>
+        <v>2882.05</v>
       </c>
       <c r="E28" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F28" t="n">
-        <v>37.85</v>
+        <v>37.82</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -1252,30 +1252,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2912.2</v>
+        <v>2847.75</v>
       </c>
       <c r="E29" t="n">
-        <v>77.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>37.72</v>
+        <v>44.08</v>
       </c>
       <c r="G29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2882.45</v>
+        <v>2844.9</v>
       </c>
       <c r="E30" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F30" t="n">
         <v>37.83</v>
@@ -1310,41 +1310,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2882.05</v>
+        <v>2843.6</v>
       </c>
       <c r="E31" t="n">
         <v>76.2</v>
       </c>
       <c r="F31" t="n">
-        <v>37.82</v>
+        <v>37.32</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lauri Markkanen</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2877.65</v>
+        <v>2817.1</v>
       </c>
       <c r="E32" t="n">
         <v>76.2</v>
       </c>
       <c r="F32" t="n">
-        <v>37.76</v>
+        <v>36.97</v>
       </c>
       <c r="G32" t="n">
         <v>29</v>
@@ -1368,12 +1368,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Damian Lillard</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1382,158 +1382,158 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2854.75</v>
+        <v>2816.4</v>
       </c>
       <c r="E33" t="n">
-        <v>65.5</v>
+        <v>77.2</v>
       </c>
       <c r="F33" t="n">
-        <v>43.58</v>
+        <v>36.48</v>
       </c>
       <c r="G33" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Walker Kessler</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2847.6</v>
+        <v>2795.7</v>
       </c>
       <c r="E34" t="n">
         <v>76.2</v>
       </c>
       <c r="F34" t="n">
-        <v>37.37</v>
+        <v>36.69</v>
       </c>
       <c r="G34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Damian Lillard</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF,C</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2823.4</v>
+        <v>2792.8</v>
       </c>
       <c r="E35" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F35" t="n">
-        <v>36.57</v>
+        <v>36.65</v>
       </c>
       <c r="G35" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Lauri Markkanen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2821.5</v>
+        <v>2785.7</v>
       </c>
       <c r="E36" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F36" t="n">
-        <v>36.55</v>
+        <v>37.04</v>
       </c>
       <c r="G36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2819.95</v>
+        <v>2781.95</v>
       </c>
       <c r="E37" t="n">
         <v>76.2</v>
       </c>
       <c r="F37" t="n">
-        <v>37.01</v>
+        <v>36.51</v>
       </c>
       <c r="G37" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SF,PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2815.3</v>
+        <v>2775.4</v>
       </c>
       <c r="E38" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F38" t="n">
-        <v>36.95</v>
+        <v>35.95</v>
       </c>
       <c r="G38" t="n">
         <v>25</v>
@@ -1542,244 +1542,244 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2799.4</v>
+        <v>2772.65</v>
       </c>
       <c r="E39" t="n">
         <v>76.2</v>
       </c>
       <c r="F39" t="n">
-        <v>36.74</v>
+        <v>36.39</v>
       </c>
       <c r="G39" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Walker Kessler</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2795.7</v>
+        <v>2766.45</v>
       </c>
       <c r="E40" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F40" t="n">
-        <v>36.69</v>
+        <v>36.79</v>
       </c>
       <c r="G40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2776.65</v>
+        <v>2712.75</v>
       </c>
       <c r="E41" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F41" t="n">
-        <v>35.97</v>
+        <v>35.6</v>
       </c>
       <c r="G41" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2775.35</v>
+        <v>2684.75</v>
       </c>
       <c r="E42" t="n">
-        <v>76.2</v>
+        <v>72.3</v>
       </c>
       <c r="F42" t="n">
-        <v>36.42</v>
+        <v>37.13</v>
       </c>
       <c r="G42" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2721.25</v>
+        <v>2680.85</v>
       </c>
       <c r="E43" t="n">
-        <v>73.3</v>
+        <v>75.2</v>
       </c>
       <c r="F43" t="n">
-        <v>37.12</v>
+        <v>35.65</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2714.55</v>
+        <v>2675.3</v>
       </c>
       <c r="E44" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F44" t="n">
-        <v>35.62</v>
+        <v>35.58</v>
       </c>
       <c r="G44" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2714.25</v>
+        <v>2656.9</v>
       </c>
       <c r="E45" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F45" t="n">
-        <v>35.62</v>
+        <v>35.33</v>
       </c>
       <c r="G45" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2709.1</v>
+        <v>2650.2</v>
       </c>
       <c r="E46" t="n">
         <v>76.2</v>
       </c>
       <c r="F46" t="n">
-        <v>35.55</v>
+        <v>34.78</v>
       </c>
       <c r="G46" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2691.95</v>
+        <v>2647.7</v>
       </c>
       <c r="E47" t="n">
         <v>76.2</v>
       </c>
       <c r="F47" t="n">
-        <v>35.33</v>
+        <v>34.75</v>
       </c>
       <c r="G47" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2674.35</v>
+        <v>2647.2</v>
       </c>
       <c r="E48" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F48" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="G48" t="n">
         <v>34</v>
@@ -1832,41 +1832,41 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Matas Buzelis</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2653.45</v>
+        <v>2630.15</v>
       </c>
       <c r="E49" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F49" t="n">
-        <v>34.82</v>
+        <v>34.98</v>
       </c>
       <c r="G49" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1875,27 +1875,27 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2649.9</v>
+        <v>2626.7</v>
       </c>
       <c r="E50" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F50" t="n">
-        <v>34.78</v>
+        <v>34.93</v>
       </c>
       <c r="G50" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1904,56 +1904,56 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2647.15</v>
+        <v>2588.05</v>
       </c>
       <c r="E51" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F51" t="n">
-        <v>34.74</v>
+        <v>34.42</v>
       </c>
       <c r="G51" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Keyonte George</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2626.5</v>
+        <v>2552.25</v>
       </c>
       <c r="E52" t="n">
         <v>75.2</v>
       </c>
       <c r="F52" t="n">
-        <v>34.93</v>
+        <v>33.94</v>
       </c>
       <c r="G52" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Ty Jerome</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1962,103 +1962,103 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2621.3</v>
+        <v>2531.8</v>
       </c>
       <c r="E53" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F53" t="n">
-        <v>34.4</v>
+        <v>33.67</v>
       </c>
       <c r="G53" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ty Jerome</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2593.1</v>
+        <v>2527.3</v>
       </c>
       <c r="E54" t="n">
         <v>76.2</v>
       </c>
       <c r="F54" t="n">
-        <v>34.03</v>
+        <v>33.17</v>
       </c>
       <c r="G54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Keyonte George</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2592.7</v>
+        <v>2525.9</v>
       </c>
       <c r="E55" t="n">
         <v>76.2</v>
       </c>
       <c r="F55" t="n">
-        <v>34.02</v>
+        <v>33.15</v>
       </c>
       <c r="G55" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2560.9</v>
+        <v>2521.5</v>
       </c>
       <c r="E56" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F56" t="n">
-        <v>33.17</v>
+        <v>33.09</v>
       </c>
       <c r="G56" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2557.85</v>
+        <v>2509.75</v>
       </c>
       <c r="E57" t="n">
-        <v>76.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>33.61</v>
+        <v>33.42</v>
       </c>
       <c r="G57" t="n">
         <v>33</v>
@@ -2093,65 +2093,65 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2533.95</v>
+        <v>2482.8</v>
       </c>
       <c r="E58" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F58" t="n">
-        <v>33.25</v>
+        <v>33.02</v>
       </c>
       <c r="G58" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2528.2</v>
+        <v>2481.75</v>
       </c>
       <c r="E59" t="n">
         <v>76.2</v>
       </c>
       <c r="F59" t="n">
-        <v>33.18</v>
+        <v>32.57</v>
       </c>
       <c r="G59" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cameron Boozer</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2161,49 +2161,49 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2527.55</v>
+        <v>2481.5</v>
       </c>
       <c r="E60" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F60" t="n">
-        <v>33.17</v>
+        <v>33</v>
       </c>
       <c r="G60" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2499.15</v>
+        <v>2475.05</v>
       </c>
       <c r="E61" t="n">
-        <v>76.2</v>
+        <v>63.4</v>
       </c>
       <c r="F61" t="n">
-        <v>32.8</v>
+        <v>39.04</v>
       </c>
       <c r="G61" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2492.6</v>
+        <v>2463.15</v>
       </c>
       <c r="E62" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F62" t="n">
-        <v>32.71</v>
+        <v>32.75</v>
       </c>
       <c r="G62" t="n">
         <v>28</v>
@@ -2238,12 +2238,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2252,74 +2252,74 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2483.75</v>
+        <v>2461.05</v>
       </c>
       <c r="E63" t="n">
         <v>76.2</v>
       </c>
       <c r="F63" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="G63" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2475.95</v>
+        <v>2446.9</v>
       </c>
       <c r="E64" t="n">
-        <v>75.2</v>
+        <v>70.3</v>
       </c>
       <c r="F64" t="n">
-        <v>32.92</v>
+        <v>34.81</v>
       </c>
       <c r="G64" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Cameron Boozer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2460.55</v>
+        <v>2441.85</v>
       </c>
       <c r="E65" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F65" t="n">
-        <v>32.29</v>
+        <v>32.47</v>
       </c>
       <c r="G65" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2451.4</v>
+        <v>2425</v>
       </c>
       <c r="E66" t="n">
-        <v>61.6</v>
+        <v>60.8</v>
       </c>
       <c r="F66" t="n">
-        <v>39.8</v>
+        <v>39.88</v>
       </c>
       <c r="G66" t="n">
         <v>34</v>
@@ -2354,99 +2354,99 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2449.9</v>
+        <v>2419.1</v>
       </c>
       <c r="E67" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F67" t="n">
-        <v>31.73</v>
+        <v>32.17</v>
       </c>
       <c r="G67" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2449.5</v>
+        <v>2416.85</v>
       </c>
       <c r="E68" t="n">
         <v>76.2</v>
       </c>
       <c r="F68" t="n">
-        <v>32.15</v>
+        <v>31.72</v>
       </c>
       <c r="G68" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2446.9</v>
+        <v>2347.3</v>
       </c>
       <c r="E69" t="n">
-        <v>70.3</v>
+        <v>76.2</v>
       </c>
       <c r="F69" t="n">
-        <v>34.81</v>
+        <v>30.8</v>
       </c>
       <c r="G69" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Caleb Wilson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2455,172 +2455,172 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2441.2</v>
+        <v>2326.85</v>
       </c>
       <c r="E70" t="n">
-        <v>64.3</v>
+        <v>75.2</v>
       </c>
       <c r="F70" t="n">
-        <v>37.97</v>
+        <v>30.94</v>
       </c>
       <c r="G70" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jaren Jackson Jr.</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2356.05</v>
+        <v>2323.4</v>
       </c>
       <c r="E71" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="F71" t="n">
-        <v>30.92</v>
+        <v>36.13</v>
       </c>
       <c r="G71" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Darius Acuff Jr.</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2355.34</v>
+        <v>2317.25</v>
       </c>
       <c r="E72" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F72" t="n">
-        <v>30.91</v>
+        <v>30.81</v>
       </c>
       <c r="G72" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2345.9</v>
+        <v>2306.9</v>
       </c>
       <c r="E73" t="n">
         <v>76.2</v>
       </c>
       <c r="F73" t="n">
-        <v>30.79</v>
+        <v>30.27</v>
       </c>
       <c r="G73" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2342.85</v>
+        <v>2304.95</v>
       </c>
       <c r="E74" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>30.75</v>
+        <v>30.29</v>
       </c>
       <c r="G74" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Day'Ron Sharpe</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2332.2</v>
+        <v>2302.25</v>
       </c>
       <c r="E75" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F75" t="n">
         <v>30.21</v>
       </c>
       <c r="G75" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ivica Zubac</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2629,56 +2629,56 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2316.5</v>
+        <v>2284.1</v>
       </c>
       <c r="E76" t="n">
         <v>75.2</v>
       </c>
       <c r="F76" t="n">
-        <v>30.8</v>
+        <v>30.37</v>
       </c>
       <c r="G76" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2315.6</v>
+        <v>2249.95</v>
       </c>
       <c r="E77" t="n">
         <v>76.2</v>
       </c>
       <c r="F77" t="n">
-        <v>30.39</v>
+        <v>29.53</v>
       </c>
       <c r="G77" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2314.6</v>
+        <v>2248.55</v>
       </c>
       <c r="E78" t="n">
-        <v>76.2</v>
+        <v>52.5</v>
       </c>
       <c r="F78" t="n">
-        <v>30.38</v>
+        <v>42.83</v>
       </c>
       <c r="G78" t="n">
         <v>24</v>
@@ -2702,41 +2702,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2304.5</v>
+        <v>2246.2</v>
       </c>
       <c r="E79" t="n">
-        <v>76.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="F79" t="n">
-        <v>30.28</v>
+        <v>29.87</v>
       </c>
       <c r="G79" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Day'Ron Sharpe</t>
+          <t>Ivica Zubac</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2745,114 +2745,114 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2301.45</v>
+        <v>2223.15</v>
       </c>
       <c r="E80" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="F80" t="n">
-        <v>30.2</v>
+        <v>29.96</v>
       </c>
       <c r="G80" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Darryn Peterson</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2277.32</v>
+        <v>2221.15</v>
       </c>
       <c r="E81" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F81" t="n">
-        <v>29.5</v>
+        <v>29.54</v>
       </c>
       <c r="G81" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fred VanVleet</t>
+          <t>Egor Dëmin</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2235.7</v>
+        <v>2212</v>
       </c>
       <c r="E82" t="n">
         <v>76.2</v>
       </c>
       <c r="F82" t="n">
-        <v>29.34</v>
+        <v>29.03</v>
       </c>
       <c r="G82" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Fred VanVleet</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2234.75</v>
+        <v>2205</v>
       </c>
       <c r="E83" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F83" t="n">
-        <v>29.33</v>
+        <v>29.32</v>
       </c>
       <c r="G83" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2861,288 +2861,288 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2223.9</v>
+        <v>2204.05</v>
       </c>
       <c r="E84" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F84" t="n">
-        <v>29.19</v>
+        <v>29.31</v>
       </c>
       <c r="G84" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Egor Dëmin</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2214.15</v>
+        <v>2193.95</v>
       </c>
       <c r="E85" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F85" t="n">
-        <v>29.06</v>
+        <v>29.17</v>
       </c>
       <c r="G85" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Jusuf Nurkić</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2207.25</v>
+        <v>2193.3</v>
       </c>
       <c r="E86" t="n">
-        <v>76.2</v>
+        <v>72.3</v>
       </c>
       <c r="F86" t="n">
-        <v>28.97</v>
+        <v>30.34</v>
       </c>
       <c r="G86" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2205.8</v>
+        <v>2189.85</v>
       </c>
       <c r="E87" t="n">
-        <v>77.2</v>
+        <v>70.3</v>
       </c>
       <c r="F87" t="n">
-        <v>28.57</v>
+        <v>31.15</v>
       </c>
       <c r="G87" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2198.95</v>
+        <v>2183.7</v>
       </c>
       <c r="E88" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F88" t="n">
-        <v>28.48</v>
+        <v>29.04</v>
       </c>
       <c r="G88" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Zach Edey</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2198.7</v>
+        <v>2171.5</v>
       </c>
       <c r="E89" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F89" t="n">
-        <v>28.85</v>
+        <v>28.88</v>
       </c>
       <c r="G89" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2194.15</v>
+        <v>2169.5</v>
       </c>
       <c r="E90" t="n">
         <v>76.2</v>
       </c>
       <c r="F90" t="n">
-        <v>28.79</v>
+        <v>28.47</v>
       </c>
       <c r="G90" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jusuf Nurkić</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2193.3</v>
+        <v>2163.1</v>
       </c>
       <c r="E91" t="n">
-        <v>72.3</v>
+        <v>76.2</v>
       </c>
       <c r="F91" t="n">
-        <v>30.34</v>
+        <v>28.39</v>
       </c>
       <c r="G91" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2189.85</v>
+        <v>2160.5</v>
       </c>
       <c r="E92" t="n">
-        <v>70.3</v>
+        <v>76.2</v>
       </c>
       <c r="F92" t="n">
-        <v>31.15</v>
+        <v>28.35</v>
       </c>
       <c r="G92" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2186.1</v>
+        <v>2157.85</v>
       </c>
       <c r="E93" t="n">
-        <v>73.3</v>
+        <v>75.2</v>
       </c>
       <c r="F93" t="n">
-        <v>29.82</v>
+        <v>28.69</v>
       </c>
       <c r="G93" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3151,74 +3151,74 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2174.7</v>
+        <v>2156.7</v>
       </c>
       <c r="E94" t="n">
-        <v>76.2</v>
+        <v>72.3</v>
       </c>
       <c r="F94" t="n">
-        <v>28.54</v>
+        <v>29.83</v>
       </c>
       <c r="G94" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2165.4</v>
+        <v>2156.4</v>
       </c>
       <c r="E95" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="F95" t="n">
-        <v>28.42</v>
+        <v>29.06</v>
       </c>
       <c r="G95" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2161.98</v>
+        <v>2154.5</v>
       </c>
       <c r="E96" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F96" t="n">
-        <v>28.37</v>
+        <v>28.65</v>
       </c>
       <c r="G96" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2141.6</v>
+        <v>2149.15</v>
       </c>
       <c r="E97" t="n">
         <v>76.2</v>
       </c>
       <c r="F97" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="G97" t="n">
         <v>20</v>
@@ -3253,59 +3253,59 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Yaxel Lendeborg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2138.3</v>
+        <v>2141.55</v>
       </c>
       <c r="E98" t="n">
         <v>75.2</v>
       </c>
       <c r="F98" t="n">
-        <v>28.43</v>
+        <v>28.48</v>
       </c>
       <c r="G98" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2137.65</v>
+        <v>2138.7</v>
       </c>
       <c r="E99" t="n">
-        <v>76.2</v>
+        <v>77</v>
       </c>
       <c r="F99" t="n">
-        <v>28.05</v>
+        <v>27.78</v>
       </c>
       <c r="G99" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2130.55</v>
+        <v>2132.1</v>
       </c>
       <c r="E100" t="n">
         <v>76.2</v>
       </c>
       <c r="F100" t="n">
-        <v>27.96</v>
+        <v>27.98</v>
       </c>
       <c r="G100" t="n">
         <v>22</v>
@@ -3340,30 +3340,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Darius Acuff Jr.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2128.55</v>
+        <v>2131.8</v>
       </c>
       <c r="E101" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F101" t="n">
-        <v>27.57</v>
+        <v>27.98</v>
       </c>
       <c r="G101" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102">
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2127.08</v>
+        <v>2130.98</v>
       </c>
       <c r="E102" t="n">
         <v>76.2</v>
       </c>
       <c r="F102" t="n">
-        <v>27.91</v>
+        <v>27.97</v>
       </c>
       <c r="G102" t="n">
         <v>30</v>
@@ -3398,268 +3398,268 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2126.85</v>
+        <v>2130.3</v>
       </c>
       <c r="E103" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F103" t="n">
-        <v>27.91</v>
+        <v>28.33</v>
       </c>
       <c r="G103" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2125</v>
+        <v>2127.1</v>
       </c>
       <c r="E104" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F104" t="n">
-        <v>27.89</v>
+        <v>27.55</v>
       </c>
       <c r="G104" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2121.8</v>
+        <v>2120.35</v>
       </c>
       <c r="E105" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F105" t="n">
-        <v>27.85</v>
+        <v>28.2</v>
       </c>
       <c r="G105" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2118.67</v>
+        <v>2116.35</v>
       </c>
       <c r="E106" t="n">
         <v>76.2</v>
       </c>
       <c r="F106" t="n">
-        <v>27.8</v>
+        <v>27.77</v>
       </c>
       <c r="G106" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2116.7</v>
+        <v>2106.85</v>
       </c>
       <c r="E107" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F107" t="n">
-        <v>27.78</v>
+        <v>27.29</v>
       </c>
       <c r="G107" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2115.35</v>
+        <v>2105.5</v>
       </c>
       <c r="E108" t="n">
-        <v>77</v>
+        <v>75.2</v>
       </c>
       <c r="F108" t="n">
-        <v>27.47</v>
+        <v>28</v>
       </c>
       <c r="G108" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2109.3</v>
+        <v>2103.4</v>
       </c>
       <c r="E109" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F109" t="n">
-        <v>27.32</v>
+        <v>27.97</v>
       </c>
       <c r="G109" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2085.7</v>
+        <v>2100.85</v>
       </c>
       <c r="E110" t="n">
-        <v>57</v>
+        <v>75.2</v>
       </c>
       <c r="F110" t="n">
-        <v>36.59</v>
+        <v>27.94</v>
       </c>
       <c r="G110" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2076.4</v>
+        <v>2094.55</v>
       </c>
       <c r="E111" t="n">
-        <v>76.2</v>
+        <v>57</v>
       </c>
       <c r="F111" t="n">
-        <v>27.25</v>
+        <v>36.75</v>
       </c>
       <c r="G111" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3669,31 +3669,31 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2076.05</v>
+        <v>2089.7</v>
       </c>
       <c r="E112" t="n">
-        <v>72.3</v>
+        <v>75.2</v>
       </c>
       <c r="F112" t="n">
-        <v>28.71</v>
+        <v>27.79</v>
       </c>
       <c r="G112" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Zach LaVine</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3702,16 +3702,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2070.2</v>
+        <v>2077.65</v>
       </c>
       <c r="E113" t="n">
         <v>76.2</v>
       </c>
       <c r="F113" t="n">
-        <v>27.17</v>
+        <v>27.27</v>
       </c>
       <c r="G113" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="114">
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2051.6</v>
+        <v>2076.45</v>
       </c>
       <c r="E114" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F114" t="n">
-        <v>26.92</v>
+        <v>27.61</v>
       </c>
       <c r="G114" t="n">
         <v>27</v>
@@ -3746,143 +3746,143 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2043.5</v>
+        <v>2076.05</v>
       </c>
       <c r="E115" t="n">
-        <v>76.2</v>
+        <v>72.3</v>
       </c>
       <c r="F115" t="n">
-        <v>26.82</v>
+        <v>28.71</v>
       </c>
       <c r="G115" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Keegan Murray</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG,SF</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2034.05</v>
+        <v>2065.65</v>
       </c>
       <c r="E116" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
       <c r="F116" t="n">
-        <v>28.53</v>
+        <v>27.11</v>
       </c>
       <c r="G116" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2032.35</v>
+        <v>2045.65</v>
       </c>
       <c r="E117" t="n">
         <v>76.2</v>
       </c>
       <c r="F117" t="n">
-        <v>26.67</v>
+        <v>26.85</v>
       </c>
       <c r="G117" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2022.9</v>
+        <v>2039.85</v>
       </c>
       <c r="E118" t="n">
-        <v>71.3</v>
+        <v>75.2</v>
       </c>
       <c r="F118" t="n">
-        <v>28.37</v>
+        <v>27.13</v>
       </c>
       <c r="G118" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Keegan Murray</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2019.25</v>
+        <v>2034.05</v>
       </c>
       <c r="E119" t="n">
-        <v>65.5</v>
+        <v>71.3</v>
       </c>
       <c r="F119" t="n">
-        <v>30.83</v>
+        <v>28.53</v>
       </c>
       <c r="G119" t="n">
         <v>26</v>
@@ -3891,268 +3891,268 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2012.5</v>
+        <v>2022.9</v>
       </c>
       <c r="E120" t="n">
-        <v>76.2</v>
+        <v>71.3</v>
       </c>
       <c r="F120" t="n">
-        <v>26.41</v>
+        <v>28.37</v>
       </c>
       <c r="G120" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2009.35</v>
+        <v>2016.75</v>
       </c>
       <c r="E121" t="n">
-        <v>77.2</v>
+        <v>65.5</v>
       </c>
       <c r="F121" t="n">
-        <v>26.03</v>
+        <v>30.79</v>
       </c>
       <c r="G121" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Zach LaVine</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PG,SG,SF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1999.65</v>
+        <v>1988.65</v>
       </c>
       <c r="E122" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F122" t="n">
-        <v>26.24</v>
+        <v>26.44</v>
       </c>
       <c r="G122" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>P.J. Washington</t>
+          <t>Ja Morant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1993.7</v>
+        <v>1987.15</v>
       </c>
       <c r="E123" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="F123" t="n">
-        <v>26.16</v>
+        <v>25.74</v>
       </c>
       <c r="G123" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ja Morant</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1990.95</v>
+        <v>1982.05</v>
       </c>
       <c r="E124" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F124" t="n">
-        <v>25.79</v>
+        <v>26.01</v>
       </c>
       <c r="G124" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1985.45</v>
+        <v>1964.6</v>
       </c>
       <c r="E125" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F125" t="n">
-        <v>26.4</v>
+        <v>25.78</v>
       </c>
       <c r="G125" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>P.J. Washington</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1977.35</v>
+        <v>1962.4</v>
       </c>
       <c r="E126" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F126" t="n">
-        <v>25.61</v>
+        <v>26.1</v>
       </c>
       <c r="G126" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1972.5</v>
+        <v>1957.55</v>
       </c>
       <c r="E127" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F127" t="n">
-        <v>25.89</v>
+        <v>26.03</v>
       </c>
       <c r="G127" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1964</v>
+        <v>1950.65</v>
       </c>
       <c r="E128" t="n">
         <v>76.2</v>
       </c>
       <c r="F128" t="n">
-        <v>25.77</v>
+        <v>25.6</v>
       </c>
       <c r="G128" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4162,31 +4162,31 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1927.85</v>
+        <v>1946.7</v>
       </c>
       <c r="E129" t="n">
         <v>76.2</v>
       </c>
       <c r="F129" t="n">
-        <v>25.3</v>
+        <v>25.55</v>
       </c>
       <c r="G129" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4195,27 +4195,27 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1889.55</v>
+        <v>1914.05</v>
       </c>
       <c r="E130" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F130" t="n">
-        <v>24.8</v>
+        <v>25.45</v>
       </c>
       <c r="G130" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4224,45 +4224,45 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1874.55</v>
+        <v>1902.2</v>
       </c>
       <c r="E131" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F131" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="G131" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1873.95</v>
+        <v>1885.25</v>
       </c>
       <c r="E132" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F132" t="n">
-        <v>24.27</v>
+        <v>24.74</v>
       </c>
       <c r="G132" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1873.05</v>
+        <v>1869.8</v>
       </c>
       <c r="E133" t="n">
         <v>77.2</v>
       </c>
       <c r="F133" t="n">
-        <v>24.26</v>
+        <v>24.22</v>
       </c>
       <c r="G133" t="n">
         <v>22</v>
@@ -4297,70 +4297,70 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Mikel Brown Jr.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1842.15</v>
+        <v>1859.75</v>
       </c>
       <c r="E134" t="n">
-        <v>62.4</v>
+        <v>76.2</v>
       </c>
       <c r="F134" t="n">
-        <v>29.52</v>
+        <v>24.41</v>
       </c>
       <c r="G134" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tre Jones</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1827.15</v>
+        <v>1850.05</v>
       </c>
       <c r="E135" t="n">
         <v>76.2</v>
       </c>
       <c r="F135" t="n">
-        <v>23.98</v>
+        <v>24.28</v>
       </c>
       <c r="G135" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4369,51 +4369,51 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1823</v>
+        <v>1835.05</v>
       </c>
       <c r="E136" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F136" t="n">
-        <v>23.61</v>
+        <v>24.4</v>
       </c>
       <c r="G136" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Jalen Smith</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1816.9</v>
+        <v>1834.35</v>
       </c>
       <c r="E137" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F137" t="n">
-        <v>23.84</v>
+        <v>24.39</v>
       </c>
       <c r="G137" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4423,205 +4423,205 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1800.15</v>
+        <v>1819.1</v>
       </c>
       <c r="E138" t="n">
-        <v>77.2</v>
+        <v>61.6</v>
       </c>
       <c r="F138" t="n">
-        <v>23.32</v>
+        <v>29.53</v>
       </c>
       <c r="G138" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ace Bailey</t>
+          <t>Tre Jones</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1795.75</v>
+        <v>1807.05</v>
       </c>
       <c r="E139" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F139" t="n">
-        <v>23.57</v>
+        <v>24.03</v>
       </c>
       <c r="G139" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1791.35</v>
+        <v>1798.35</v>
       </c>
       <c r="E140" t="n">
         <v>76.2</v>
       </c>
       <c r="F140" t="n">
-        <v>23.51</v>
+        <v>23.6</v>
       </c>
       <c r="G140" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Jalen Smith</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1781.3</v>
+        <v>1788.45</v>
       </c>
       <c r="E141" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F141" t="n">
-        <v>23.38</v>
+        <v>23.78</v>
       </c>
       <c r="G141" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Ace Bailey</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1768.2</v>
+        <v>1787.15</v>
       </c>
       <c r="E142" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F142" t="n">
-        <v>23.2</v>
+        <v>23.77</v>
       </c>
       <c r="G142" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1761.3</v>
+        <v>1778.2</v>
       </c>
       <c r="E143" t="n">
         <v>76.2</v>
       </c>
       <c r="F143" t="n">
-        <v>23.11</v>
+        <v>23.34</v>
       </c>
       <c r="G143" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Khaman Maluach</t>
+          <t>AJ Dybantsa</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1754.5</v>
+        <v>1776.75</v>
       </c>
       <c r="E144" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F144" t="n">
-        <v>22.73</v>
+        <v>23.63</v>
       </c>
       <c r="G144" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Jaylen Wells</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1747.6</v>
+        <v>1747.05</v>
       </c>
       <c r="E145" t="n">
         <v>76.2</v>
@@ -4639,149 +4639,149 @@
         <v>22.93</v>
       </c>
       <c r="G145" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1729.65</v>
+        <v>1744.65</v>
       </c>
       <c r="E146" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F146" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="G146" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711.5</v>
+        <v>1726.3</v>
       </c>
       <c r="E147" t="n">
         <v>76.2</v>
       </c>
       <c r="F147" t="n">
-        <v>22.46</v>
+        <v>22.65</v>
       </c>
       <c r="G147" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Khaman Maluach</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1693.1</v>
+        <v>1722.85</v>
       </c>
       <c r="E148" t="n">
         <v>76.2</v>
       </c>
       <c r="F148" t="n">
-        <v>22.22</v>
+        <v>22.61</v>
       </c>
       <c r="G148" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bobby Portis Jr.</t>
+          <t>Jaylen Wells</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1679.35</v>
+        <v>1717.8</v>
       </c>
       <c r="E149" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F149" t="n">
-        <v>22.04</v>
+        <v>22.84</v>
       </c>
       <c r="G149" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1640.45</v>
+        <v>1711.4</v>
       </c>
       <c r="E150" t="n">
         <v>76.2</v>
       </c>
       <c r="F150" t="n">
-        <v>21.53</v>
+        <v>22.46</v>
       </c>
       <c r="G150" t="n">
         <v>26</v>
@@ -4790,7 +4790,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kyle Filipowski</t>
+          <t>Jaren Jackson Jr.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4804,56 +4804,56 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1636.1</v>
+        <v>1708.35</v>
       </c>
       <c r="E151" t="n">
-        <v>76.2</v>
+        <v>55.4</v>
       </c>
       <c r="F151" t="n">
-        <v>21.47</v>
+        <v>30.84</v>
       </c>
       <c r="G151" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Keaton Wagler</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1628.45</v>
+        <v>1706.05</v>
       </c>
       <c r="E152" t="n">
         <v>76.2</v>
       </c>
       <c r="F152" t="n">
-        <v>21.37</v>
+        <v>22.39</v>
       </c>
       <c r="G152" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4862,27 +4862,27 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1627.1</v>
+        <v>1705</v>
       </c>
       <c r="E153" t="n">
         <v>76.2</v>
       </c>
       <c r="F153" t="n">
-        <v>21.35</v>
+        <v>22.38</v>
       </c>
       <c r="G153" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4891,27 +4891,27 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1614.65</v>
+        <v>1675.35</v>
       </c>
       <c r="E154" t="n">
-        <v>77.2</v>
+        <v>75.2</v>
       </c>
       <c r="F154" t="n">
-        <v>20.92</v>
+        <v>22.28</v>
       </c>
       <c r="G154" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Bobby Portis Jr.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4920,103 +4920,103 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1613.1</v>
+        <v>1653.28</v>
       </c>
       <c r="E155" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F155" t="n">
-        <v>21.17</v>
+        <v>21.99</v>
       </c>
       <c r="G155" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1612.3</v>
+        <v>1641.4</v>
       </c>
       <c r="E156" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F156" t="n">
-        <v>20.88</v>
+        <v>21.54</v>
       </c>
       <c r="G156" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1607.8</v>
+        <v>1612.75</v>
       </c>
       <c r="E157" t="n">
         <v>76.2</v>
       </c>
       <c r="F157" t="n">
-        <v>21.1</v>
+        <v>21.16</v>
       </c>
       <c r="G157" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1597.95</v>
+        <v>1604.38</v>
       </c>
       <c r="E158" t="n">
-        <v>73.3</v>
+        <v>75.2</v>
       </c>
       <c r="F158" t="n">
-        <v>21.8</v>
+        <v>21.33</v>
       </c>
       <c r="G158" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="159">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1591.8</v>
+        <v>1603.55</v>
       </c>
       <c r="E159" t="n">
         <v>76.2</v>
       </c>
       <c r="F159" t="n">
-        <v>20.89</v>
+        <v>21.04</v>
       </c>
       <c r="G159" t="n">
         <v>24</v>
@@ -5051,12 +5051,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5065,225 +5065,225 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1591.5</v>
+        <v>1597.95</v>
       </c>
       <c r="E160" t="n">
-        <v>75.2</v>
+        <v>73.3</v>
       </c>
       <c r="F160" t="n">
-        <v>21.16</v>
+        <v>21.8</v>
       </c>
       <c r="G160" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1579.65</v>
+        <v>1596.58</v>
       </c>
       <c r="E161" t="n">
-        <v>77.2</v>
+        <v>76.2</v>
       </c>
       <c r="F161" t="n">
-        <v>20.46</v>
+        <v>20.95</v>
       </c>
       <c r="G161" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1560.55</v>
+        <v>1593.2</v>
       </c>
       <c r="E162" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F162" t="n">
-        <v>20.48</v>
+        <v>21.19</v>
       </c>
       <c r="G162" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF,PF</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1557.85</v>
+        <v>1592.65</v>
       </c>
       <c r="E163" t="n">
         <v>76.2</v>
       </c>
       <c r="F163" t="n">
-        <v>20.44</v>
+        <v>20.9</v>
       </c>
       <c r="G163" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1556.2</v>
+        <v>1583.4</v>
       </c>
       <c r="E164" t="n">
-        <v>73.3</v>
+        <v>75.2</v>
       </c>
       <c r="F164" t="n">
-        <v>21.23</v>
+        <v>21.06</v>
       </c>
       <c r="G164" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1551.05</v>
+        <v>1569.3</v>
       </c>
       <c r="E165" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="F165" t="n">
-        <v>20.35</v>
+        <v>21.15</v>
       </c>
       <c r="G165" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1529.55</v>
+        <v>1567.3</v>
       </c>
       <c r="E166" t="n">
         <v>76.2</v>
       </c>
       <c r="F166" t="n">
-        <v>20.07</v>
+        <v>20.57</v>
       </c>
       <c r="G166" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PG,SG</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1526.65</v>
+        <v>1566.15</v>
       </c>
       <c r="E167" t="n">
         <v>76.2</v>
       </c>
       <c r="F167" t="n">
-        <v>20.03</v>
+        <v>20.55</v>
       </c>
       <c r="G167" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5293,338 +5293,280 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1521.95</v>
+        <v>1563.35</v>
       </c>
       <c r="E168" t="n">
         <v>76.2</v>
       </c>
       <c r="F168" t="n">
-        <v>19.97</v>
+        <v>20.52</v>
       </c>
       <c r="G168" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>De'Andre Hunter</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>PF,C</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1517.5</v>
+        <v>1557.1</v>
       </c>
       <c r="E169" t="n">
         <v>76.2</v>
       </c>
       <c r="F169" t="n">
-        <v>19.91</v>
+        <v>20.43</v>
       </c>
       <c r="G169" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SG,SF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1511.8</v>
+        <v>1556.2</v>
       </c>
       <c r="E170" t="n">
-        <v>76.2</v>
+        <v>73.3</v>
       </c>
       <c r="F170" t="n">
-        <v>19.84</v>
+        <v>21.23</v>
       </c>
       <c r="G170" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SF,PF</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1509.95</v>
+        <v>1527.1</v>
       </c>
       <c r="E171" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F171" t="n">
-        <v>19.82</v>
+        <v>20.31</v>
       </c>
       <c r="G171" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Kyshawn George</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1503.7</v>
+        <v>1525.9</v>
       </c>
       <c r="E172" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F172" t="n">
-        <v>19.73</v>
+        <v>20.29</v>
       </c>
       <c r="G172" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Scotty Pippen Jr.</t>
+          <t>De'Andre Hunter</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SF,PF</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1492.1</v>
+        <v>1518.7</v>
       </c>
       <c r="E173" t="n">
         <v>76.2</v>
       </c>
       <c r="F173" t="n">
-        <v>19.58</v>
+        <v>19.93</v>
       </c>
       <c r="G173" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SG,SF,PF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1490.58</v>
+        <v>1512.35</v>
       </c>
       <c r="E174" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F174" t="n">
-        <v>19.56</v>
+        <v>20.11</v>
       </c>
       <c r="G174" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Kristaps Porziņģis</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1484.8</v>
+        <v>1507.3</v>
       </c>
       <c r="E175" t="n">
-        <v>59.4</v>
+        <v>75.2</v>
       </c>
       <c r="F175" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="G175" t="n">
         <v>25</v>
-      </c>
-      <c r="G175" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PF,C</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1484.8</v>
+        <v>1489.6</v>
       </c>
       <c r="E176" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F176" t="n">
-        <v>19.49</v>
+        <v>19.81</v>
       </c>
       <c r="G176" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PG,SG</t>
+          <t>SG,SF</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1476.9</v>
+        <v>1032.85</v>
       </c>
       <c r="E177" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="F177" t="n">
-        <v>19.38</v>
+        <v>13.73</v>
       </c>
       <c r="G177" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Derrick Jones Jr.</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>SF,PF</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>1467.05</v>
-      </c>
-      <c r="E178" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="F178" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="G178" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Aaron Wiggins</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>SG,SF</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>1056.7</v>
-      </c>
-      <c r="E179" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="G179" t="n">
         <v>28</v>
       </c>
     </row>
@@ -5662,7 +5604,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90a77af709458880df7c2613a030ae4c3020e840c4eb3748457579938ccde3ed</t>
+          <t>298e203cfcaac6cbea15f0c188860586fc3f7cd4f5cacaa0f7eaf7aeff4a582b</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5616,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T22:09:19</t>
+          <t>2026-10-28T00:30:05</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5628,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"applied": [{"now": {"player_proj_GP": 76.2, "player_total_proj_FP": 2527.55, "projectedFPPG": 33.17}, "player_name": "Cameron Boozer", "reason": "Yahoo's rest-of-season view (S_PSR) reports 0 GP / 0.00 FP for a healthy rostered player (Benton)", "replaces": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0}, "replaces_matches": true, "review_by": "2026-11-03", "yahoo": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0, "projectedFPPG": 0.0}, "yahoo_id": "10592"}, {"now": {"player_proj_GP": 76.2, "player_total_proj_FP": 2355.34, "projectedFPPG": 30.91}, "player_name": "Darius Acuff Jr.", "reason": "Yahoo's rest-of-season view (S_PSR) reports 0 GP / 0.00 FP for a healthy rostered player (Hayden)", "replaces": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0}, "replaces_matches": true, "review_by": "2026-11-03", "yahoo": {"player_proj_GP": 0.0, "player_total_proj_FP": 0.0, "projectedFPPG": 0.0}, "yahoo_id": "10582"}], "unapplied": []}</t>
+          <t>{"applied": [], "unapplied": []}</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5639,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
